--- a/results/job_matches_2026-07-25.xlsx
+++ b/results/job_matches_2026-07-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Azure Cloud Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cloud and Things</t>
+          <t>Inadev Corporation</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>19.4</v>
+        <v>20.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, Event Hubs</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e5bb3180486d837</t>
+          <t>https://www.indeed.com/viewjob?jk=c81a4ee6ef1c78d4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer III-Databricks</t>
+          <t>Azure Cloud Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, Event Hubs</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=097f3e8cd3b1164b</t>
+          <t>https://www.indeed.com/viewjob?jk=6e5bb3180486d837</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer for Patient Safety Measure Engine</t>
+          <t>Software Engineer III-Databricks</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,42 +566,42 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d3f3d22744f5363</t>
+          <t>https://www.indeed.com/viewjob?jk=097f3e8cd3b1164b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior GCP Data Engineer for Patient Safety Measure Engine</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Continuum Media Network Inc</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, ECS, RDS, Azure, GCP, Scala, SQL Server, MySQL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d00a5640ed9db41</t>
+          <t>https://www.indeed.com/viewjob?jk=6d3f3d22744f5363</t>
         </is>
       </c>
     </row>
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AWS Cloud Architect</t>
+          <t>Sr. Engineer, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cloud and Things</t>
+          <t>Lovesac</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, Splunk, CI/CD</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Medallion Architecture, BigQuery, Dataflow, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3a616293a442292</t>
+          <t>https://www.indeed.com/viewjob?jk=2d666b2674d51e46</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior AI DevOps Engineer (AI Ops / Platform Engineering) (Hybrid)</t>
+          <t>AWS Cloud Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,17 +696,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Scala, Splunk, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179f845817d9c394</t>
+          <t>https://www.indeed.com/viewjob?jk=e3a616293a442292</t>
         </is>
       </c>
     </row>
@@ -783,25 +783,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Cloud DBA</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CMG Financial</t>
+          <t>Gradera</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Hive, Spark, Snowflake, SQL Server, PostgreSQL, ELT, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73905ae2a449372f</t>
+          <t>https://www.indeed.com/viewjob?jk=0f26c60aecfc298d</t>
         </is>
       </c>
     </row>
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data engineer (Power BI)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>TAIT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Lititz, PA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Snowflake, Oracle</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1c4bb478a10661f</t>
+          <t>https://www.indeed.com/viewjob?jk=54cfb968de0a9abd</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data engineer (Power BI)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pyx Health</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea50071b5800db9</t>
+          <t>https://www.indeed.com/viewjob?jk=b1c4bb478a10661f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Developer, Automation</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FFF Enterprises</t>
+          <t>Pyx Health</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Temecula, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36278831392884e9</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea50071b5800db9</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Versa Networks</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, GCP, Cloud Storage, Spark, Scala, Dask, Data Modeling, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=630d48996f1eac48</t>
+          <t>https://www.indeed.com/viewjob?jk=f6cd7a40acf5c8ea</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Versa Networks</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,17 +1081,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Dask, Polars, MLOps, MLflow, Terraform</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7a92b5805d6137</t>
+          <t>https://www.indeed.com/viewjob?jk=6d8fd3bb26a1e48b</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd3e9bf3427fd2d6</t>
+          <t>https://www.indeed.com/viewjob?jk=630d48996f1eac48</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ec6e06ec6b6e3fa</t>
+          <t>https://www.indeed.com/viewjob?jk=9d7a92b5805d6137</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14216a18b53ccbd9</t>
+          <t>https://www.indeed.com/viewjob?jk=fd3e9bf3427fd2d6</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4bf15647e9f22c6</t>
+          <t>https://www.indeed.com/viewjob?jk=3ec6e06ec6b6e3fa</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Surescripts</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4bcd6e2a9d67464</t>
+          <t>https://www.indeed.com/viewjob?jk=14216a18b53ccbd9</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d0c84a27d084fd0</t>
+          <t>https://www.indeed.com/viewjob?jk=c4bf15647e9f22c6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>Surescripts</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcbdf62f4fcd37bb</t>
+          <t>https://www.indeed.com/viewjob?jk=d4bcd6e2a9d67464</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>First Citizens Bank</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ac40ad9509eb3e</t>
+          <t>https://www.indeed.com/viewjob?jk=8d0c84a27d084fd0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AWS/EKS Platform Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Glint Tech Solutions</t>
+          <t>First Citizens Bank</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1db2cf8626316dc6</t>
+          <t>https://www.indeed.com/viewjob?jk=34ac40ad9509eb3e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior IT Developer TDS (US)</t>
+          <t>AWS/EKS Platform Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Kafka, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ba9067ff8ad3678</t>
+          <t>https://www.indeed.com/viewjob?jk=1db2cf8626316dc6</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (33139)</t>
+          <t>Senior IT Developer TDS (US)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Scala, Kafka, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f6d6b581aa01dfb</t>
+          <t>https://www.indeed.com/viewjob?jk=4ba9067ff8ad3678</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior MarTech Engineer (Braze/Claude)</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da2cd5f2d2247bd7</t>
+          <t>https://www.indeed.com/viewjob?jk=8e283e1b09898d08</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Senior Analytics Engineer (33139)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3949515f70fcddc9</t>
+          <t>https://www.indeed.com/viewjob?jk=9f6d6b581aa01dfb</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Senior MarTech Engineer (Braze/Claude)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,42 +1571,42 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c47582fc7c2ae03</t>
+          <t>https://www.indeed.com/viewjob?jk=da2cd5f2d2247bd7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, MySQL, MongoDB</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7424c005b9ced1ab</t>
+          <t>https://www.indeed.com/viewjob?jk=3949515f70fcddc9</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer - Delivery DevOps</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f60289bd7b154e2</t>
+          <t>https://www.indeed.com/viewjob?jk=ac326e94203a756e</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Centerprism</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b3e11011f10bd71</t>
+          <t>https://www.indeed.com/viewjob?jk=7424c005b9ced1ab</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Senior Systems Engineer - Delivery DevOps</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, BigQuery, Scala, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0600fe838e8fd40</t>
+          <t>https://www.indeed.com/viewjob?jk=7f60289bd7b154e2</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Forward Deployed Software Engineer (FDE)</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Zebra Technologies</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Holtsville, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,17 +1746,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb34fa941aa1af4f</t>
+          <t>https://www.indeed.com/viewjob?jk=a0600fe838e8fd40</t>
         </is>
       </c>
     </row>
@@ -1833,17 +1833,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AI Solutions Architect | US</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cuesta Partners</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,17 +1851,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, Snowflake, Data Modeling, MLflow</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96a29f61f02164cc</t>
+          <t>https://www.indeed.com/viewjob?jk=1b73563a16146db3</t>
         </is>
       </c>
     </row>
@@ -1903,17 +1903,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Liquidity Services, Inc.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>AWS, Redshift, Azure, BigQuery, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcc108d020014d64</t>
+          <t>https://www.indeed.com/viewjob?jk=faf4368f99c56fa7</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cronisys IT LLC</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b7d3c5854895a0d</t>
+          <t>https://www.indeed.com/viewjob?jk=fcc108d020014d64</t>
         </is>
       </c>
     </row>
@@ -2288,17 +2288,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer-Data Operations (Databricks/AI)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>H&amp;R Block</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22eb530ec4c57c3c</t>
+          <t>https://www.indeed.com/viewjob?jk=096cfd68dbda7a1a</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Business Systems Engineer</t>
+          <t>Senior Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Frank Darling</t>
+          <t>Ingram Micro</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, DynamoDB, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d75b0168c3af177d</t>
+          <t>https://www.indeed.com/viewjob?jk=1fbe4faecbcb6e49</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
+          <t>AWS &amp; Databricks Platform Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Simpson Strong-Tie</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b066ce08bf22f47c</t>
+          <t>https://www.indeed.com/viewjob?jk=54ffcf229826c509</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Java AWS Software Engineer III</t>
+          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Simpson Strong-Tie</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e88dcde57fa9ced</t>
+          <t>https://www.indeed.com/viewjob?jk=b066ce08bf22f47c</t>
         </is>
       </c>
     </row>
@@ -2603,12 +2603,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Pre-Sales Solution Architect</t>
+          <t>Business Systems Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Blue Orange Digital</t>
+          <t>Frank Darling</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Snowflake, ELT, dbt</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=148c58d976f8aa98</t>
+          <t>https://www.indeed.com/viewjob?jk=d75b0168c3af177d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer III - Full Stack ReactJS, Java, Python, AWS + Monday.com Platform</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Precisely</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Databricks, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e21285074de6c55</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3498d244cd3dd0</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Java AWS Software Engineer III</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Precisely</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3498d244cd3dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=7e88dcde57fa9ced</t>
         </is>
       </c>
     </row>
@@ -2778,25 +2778,25 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer II (Python/Java/AWS/Pyspark)</t>
+          <t>Senior Pre-Sales Solution Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Blue Orange Digital</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Star Schema, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Snowflake, ELT, dbt</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee9a97ffa509cdb3</t>
+          <t>https://www.indeed.com/viewjob?jk=148c58d976f8aa98</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Software Engineer III - Full Stack ReactJS, Java, Python, AWS + Monday.com Platform</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Axogen</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Fact Tables, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Databricks, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24d477b9eaa3792d</t>
+          <t>https://www.indeed.com/viewjob?jk=8e21285074de6c55</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Analyst / Engineer</t>
+          <t>Data DevOps Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Versa Networks</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, Jenkins, Terraform, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fb24a781dd0a7af</t>
+          <t>https://www.indeed.com/viewjob?jk=6e80fc4f1c8a9728</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>DERMS Data Architect &amp; Integration</t>
+          <t>Software Engineer II (Python/Java/AWS/Pyspark)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GE Vernova</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Star Schema, CI/CD, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=381bad2f60317342</t>
+          <t>https://www.indeed.com/viewjob?jk=ee9a97ffa509cdb3</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Axogen</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, Git</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Fact Tables, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=935ece4128fe6f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=24d477b9eaa3792d</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Java Application Architect</t>
+          <t>Data Analyst / Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=961ed4e278a33edd</t>
+          <t>https://www.indeed.com/viewjob?jk=9fb24a781dd0a7af</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Business Informatics Support Data Engineer</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Trillium Health Resources</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
+          <t>RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1bc5a017b98965e</t>
+          <t>https://www.indeed.com/viewjob?jk=099ab57136f08627</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Business Informatics Support Data Engineer</t>
+          <t>DERMS Data Architect &amp; Integration</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Trillium Health Resources</t>
+          <t>GE Vernova</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61b3b18503d4acec</t>
+          <t>https://www.indeed.com/viewjob?jk=381bad2f60317342</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer III - (Pyspark/databricks/Mongo/Sql/Python)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=820ae5b00199f1e8</t>
+          <t>https://www.indeed.com/viewjob?jk=935ece4128fe6f9f</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Quality Assurance Specialist</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>RELI Group Inc</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3691bd3a3b5f022b</t>
+          <t>https://www.indeed.com/viewjob?jk=e0047e52c4d67e20</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Great Gray Trust Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, Docker, SonarQube, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d12b3ac28ec908f</t>
+          <t>https://www.indeed.com/viewjob?jk=b91b81ba111bb33b</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer – Full Stack</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Empower Pharmacy</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,17 +3181,262 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7afb773581c3b4c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer II - Encore Program</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Hermitage, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=95650589278c6f55</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer II - Encore Program</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2f93e37daf3e792</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Business Informatics Support Data Engineer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Trillium Health Resources</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1bc5a017b98965e</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Business Informatics Support Data Engineer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Trillium Health Resources</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61b3b18503d4acec</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Data Engineer III - (Pyspark/databricks/Mongo/Sql/Python)</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=820ae5b00199f1e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Software Engineer – Full Stack</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Empower Pharmacy</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=e06173fc3c6ce8f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Great Gray Trust Company</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, Docker, SonarQube, Git, Python</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d12b3ac28ec908f</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-25.xlsx
+++ b/results/job_matches_2026-07-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Platform Engineer VI - Data Services</t>
+          <t>Data Engineer- Analytics Products</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>DC PUBLIC CHARTER SCHOOL BOARD</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=530025f520e267c1</t>
+          <t>https://www.indeed.com/viewjob?jk=6722d6963193ac95</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Platform Engineer VI - Data Services</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TAIT</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lititz, PA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54cfb968de0a9abd</t>
+          <t>https://www.indeed.com/viewjob?jk=530025f520e267c1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data engineer (Power BI)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>TAIT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Lititz, PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Snowflake, Oracle</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1c4bb478a10661f</t>
+          <t>https://www.indeed.com/viewjob?jk=54cfb968de0a9abd</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data engineer (Power BI)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pyx Health</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,19 +951,19 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea50071b5800db9</t>
+          <t>https://www.indeed.com/viewjob?jk=b1c4bb478a10661f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Pyx Health</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -972,11 +972,11 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d24836d15aa901f</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea50071b5800db9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Scientist Senior Associate</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, RDS, Spark, PySpark, Oracle, ETL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,94 +1021,94 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c02b7e5e2ede6f3</t>
+          <t>https://www.indeed.com/viewjob?jk=6d24836d15aa901f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Data Scientist Senior Associate</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Versa Networks</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, GCP, Cloud Storage, Spark, Scala, Dask, Data Modeling, CI/CD, Terraform, Docker</t>
+          <t>AWS, Glue, ECS, RDS, Spark, PySpark, Oracle, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6cd7a40acf5c8ea</t>
+          <t>https://www.indeed.com/viewjob?jk=8c02b7e5e2ede6f3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>DevOps Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Versa Networks</t>
+          <t>Unlimited Systems</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Dask, Polars, MLOps, MLflow, Terraform</t>
+          <t>AWS, SQS, API Gateway, ECS, IAM, RDS, Azure, Scala, Kafka, Splunk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d8fd3bb26a1e48b</t>
+          <t>https://www.indeed.com/viewjob?jk=e19d2be5d242f190</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Versa Networks</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, GCP, Cloud Storage, Spark, Scala, Dask, Data Modeling, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=630d48996f1eac48</t>
+          <t>https://www.indeed.com/viewjob?jk=f6cd7a40acf5c8ea</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Versa Networks</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Dask, Polars, MLOps, MLflow, Terraform</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7a92b5805d6137</t>
+          <t>https://www.indeed.com/viewjob?jk=6d8fd3bb26a1e48b</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd3e9bf3427fd2d6</t>
+          <t>https://www.indeed.com/viewjob?jk=630d48996f1eac48</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ec6e06ec6b6e3fa</t>
+          <t>https://www.indeed.com/viewjob?jk=9d7a92b5805d6137</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14216a18b53ccbd9</t>
+          <t>https://www.indeed.com/viewjob?jk=fd3e9bf3427fd2d6</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4bf15647e9f22c6</t>
+          <t>https://www.indeed.com/viewjob?jk=3ec6e06ec6b6e3fa</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Surescripts</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4bcd6e2a9d67464</t>
+          <t>https://www.indeed.com/viewjob?jk=14216a18b53ccbd9</t>
         </is>
       </c>
     </row>
@@ -1348,12 +1348,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,19 +1371,19 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d0c84a27d084fd0</t>
+          <t>https://www.indeed.com/viewjob?jk=c4bf15647e9f22c6</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>First Citizens Bank</t>
+          <t>Surescripts</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ac40ad9509eb3e</t>
+          <t>https://www.indeed.com/viewjob?jk=d4bcd6e2a9d67464</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AWS/EKS Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Glint Tech Solutions</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1db2cf8626316dc6</t>
+          <t>https://www.indeed.com/viewjob?jk=8d0c84a27d084fd0</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior IT Developer TDS (US)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>First Citizens Bank</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Kafka, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ba9067ff8ad3678</t>
+          <t>https://www.indeed.com/viewjob?jk=34ac40ad9509eb3e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>Senior IT Developer TDS (US)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Databricks, Scala, Kafka, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e283e1b09898d08</t>
+          <t>https://www.indeed.com/viewjob?jk=4ba9067ff8ad3678</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (33139)</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f6d6b581aa01dfb</t>
+          <t>https://www.indeed.com/viewjob?jk=8e283e1b09898d08</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior MarTech Engineer (Braze/Claude)</t>
+          <t>Senior Analytics Engineer (33139)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da2cd5f2d2247bd7</t>
+          <t>https://www.indeed.com/viewjob?jk=9f6d6b581aa01dfb</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Senior MarTech Engineer (Braze/Claude)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,42 +1606,42 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3949515f70fcddc9</t>
+          <t>https://www.indeed.com/viewjob?jk=da2cd5f2d2247bd7</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, MySQL, MongoDB</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac326e94203a756e</t>
+          <t>https://www.indeed.com/viewjob?jk=3949515f70fcddc9</t>
         </is>
       </c>
     </row>
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7424c005b9ced1ab</t>
+          <t>https://www.indeed.com/viewjob?jk=ac326e94203a756e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer - Delivery DevOps</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f60289bd7b154e2</t>
+          <t>https://www.indeed.com/viewjob?jk=7424c005b9ced1ab</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Senior Systems Engineer - Delivery DevOps</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, BigQuery, Scala, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0600fe838e8fd40</t>
+          <t>https://www.indeed.com/viewjob?jk=7f60289bd7b154e2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer III - Cloud Data Platform</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26ac8e996e1bb5d6</t>
+          <t>https://www.indeed.com/viewjob?jk=a0600fe838e8fd40</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Associate Cloud &amp; DevOps Engineer</t>
+          <t>Software Engineer III - Cloud Data Platform</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>First Orion</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>North Little Rock, AR, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, SQS, IAM, RDS, Scala, DynamoDB, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f4ff182033422db</t>
+          <t>https://www.indeed.com/viewjob?jk=26ac8e996e1bb5d6</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Sr. Software Engineer, Cloud - Analytics Platform</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Spark, Scala, MySQL, DynamoDB, Cassandra, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b73563a16146db3</t>
+          <t>https://www.indeed.com/viewjob?jk=ec75113b2386de94</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4beac6cc3645a53b</t>
+          <t>https://www.indeed.com/viewjob?jk=1b73563a16146db3</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Liquidity Services, Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, BigQuery, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf4368f99c56fa7</t>
+          <t>https://www.indeed.com/viewjob?jk=4beac6cc3645a53b</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Liquidity Services, Inc.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>AWS, Redshift, Azure, BigQuery, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcc108d020014d64</t>
+          <t>https://www.indeed.com/viewjob?jk=faf4368f99c56fa7</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>One Call</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=454dc6c270b9d674</t>
+          <t>https://www.indeed.com/viewjob?jk=fcc108d020014d64</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>One Call</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13f9bc74bc5d1d66</t>
+          <t>https://www.indeed.com/viewjob?jk=454dc6c270b9d674</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Sally Beauty</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5832467cbe11eede</t>
+          <t>https://www.indeed.com/viewjob?jk=13f9bc74bc5d1d66</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer II-Python/PySpark</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Sally Beauty</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
+          <t>RDS, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbbc18e6ff889804</t>
+          <t>https://www.indeed.com/viewjob?jk=5832467cbe11eede</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Software Engineer II-Python/PySpark</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76545a7a26014492</t>
+          <t>https://www.indeed.com/viewjob?jk=bbbc18e6ff889804</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Platform &amp; Integration Engineer (Kafka)</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Medica Services Company LLC</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, ECS, IAM, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a1e479ebfe2163b</t>
+          <t>https://www.indeed.com/viewjob?jk=76545a7a26014492</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Cloud &amp; AI Platform)- Remote within US</t>
+          <t>Senior Platform &amp; Integration Engineer (Kafka)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>OEConnection</t>
+          <t>Medica Services Company LLC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=024ce94c4237b353</t>
+          <t>https://www.indeed.com/viewjob?jk=1a1e479ebfe2163b</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e08d2c63dac884c6</t>
+          <t>https://www.indeed.com/viewjob?jk=024ce94c4237b353</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Clinical Data Engineer (Application Engineer)</t>
+          <t>Senior Platform Engineer (Cloud &amp; AI Platform)- Remote within US</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Oregon Health &amp; Science University</t>
+          <t>OEConnection</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Azure, Medallion Architecture, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL, Azure DevOps, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4baa56a62cb41945</t>
+          <t>https://www.indeed.com/viewjob?jk=e08d2c63dac884c6</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Clinical Data Engineer (Application Engineer)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>Oregon Health &amp; Science University</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
+          <t>Azure, Medallion Architecture, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=096cfd68dbda7a1a</t>
+          <t>https://www.indeed.com/viewjob?jk=4baa56a62cb41945</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Agentic AI Engineer</t>
+          <t>Senior Java Developer with AI Experience</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ingram Micro</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Dask, CI/CD, Git</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fbe4faecbcb6e49</t>
+          <t>https://www.indeed.com/viewjob?jk=c1f24944a225af1c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AWS &amp; Databricks Platform Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54ffcf229826c509</t>
+          <t>https://www.indeed.com/viewjob?jk=096cfd68dbda7a1a</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
+          <t>Senior Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Simpson Strong-Tie</t>
+          <t>Ingram Micro</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b066ce08bf22f47c</t>
+          <t>https://www.indeed.com/viewjob?jk=1fbe4faecbcb6e49</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Architect</t>
+          <t>AWS &amp; Databricks Platform Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>M2S Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Highland Park, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dde1cd623d007554</t>
+          <t>https://www.indeed.com/viewjob?jk=54ffcf229826c509</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BGE, Inc</t>
+          <t>Simpson Strong-Tie</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c4f37450aa9007</t>
+          <t>https://www.indeed.com/viewjob?jk=b066ce08bf22f47c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Artificial Intelligence Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BGE, Inc</t>
+          <t>M2S Group</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Highland Park, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ed66eb1c43b3061</t>
+          <t>https://www.indeed.com/viewjob?jk=dde1cd623d007554</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4f5eb1da717e31e</t>
+          <t>https://www.indeed.com/viewjob?jk=54c4f37450aa9007</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PURE Insurance</t>
+          <t>BGE, Inc</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>White Plains, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, Scala, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b7ea8b8e5406480</t>
+          <t>https://www.indeed.com/viewjob?jk=1ed66eb1c43b3061</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Business Systems Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Frank Darling</t>
+          <t>BGE, Inc</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, DynamoDB, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d75b0168c3af177d</t>
+          <t>https://www.indeed.com/viewjob?jk=b4f5eb1da717e31e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Precisely</t>
+          <t>PURE Insurance</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>White Plains, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Databricks, Scala, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,19 +2666,19 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3498d244cd3dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=2b7ea8b8e5406480</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Java AWS Software Engineer III</t>
+          <t>Business Systems Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Frank Darling</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e88dcde57fa9ced</t>
+          <t>https://www.indeed.com/viewjob?jk=d75b0168c3af177d</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Senior Pre-Sales Solution Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>Blue Orange Digital</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, MySQL, ETL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Snowflake, ELT, dbt</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77de33f1323a932a</t>
+          <t>https://www.indeed.com/viewjob?jk=148c58d976f8aa98</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Software Engineer III - Full Stack ReactJS, Java, Python, AWS + Monday.com Platform</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, MySQL, ETL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Databricks, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fca0033255b9f7dc</t>
+          <t>https://www.indeed.com/viewjob?jk=8e21285074de6c55</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Pre-Sales Solution Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Blue Orange Digital</t>
+          <t>Precisely</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Snowflake, ELT, dbt</t>
+          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,14 +2806,14 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=148c58d976f8aa98</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3498d244cd3dd0</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer III - Full Stack ReactJS, Java, Python, AWS + Monday.com Platform</t>
+          <t>Java AWS Software Engineer III</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Databricks, Scala, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,67 +2841,67 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e21285074de6c55</t>
+          <t>https://www.indeed.com/viewjob?jk=7e88dcde57fa9ced</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data DevOps Engineer</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Versa Networks</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, Jenkins, Terraform, Jenkins, Git, Python</t>
+          <t>AWS, Azure, Scala, SQL Server, MySQL, ETL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e80fc4f1c8a9728</t>
+          <t>https://www.indeed.com/viewjob?jk=77de33f1323a932a</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer II (Python/Java/AWS/Pyspark)</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Star Schema, CI/CD, Git</t>
+          <t>AWS, Azure, Scala, SQL Server, MySQL, ETL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee9a97ffa509cdb3</t>
+          <t>https://www.indeed.com/viewjob?jk=fca0033255b9f7dc</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Data DevOps Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Axogen</t>
+          <t>Versa Networks</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Fact Tables, Power BI, CI/CD, Azure DevOps</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, Jenkins, Terraform, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24d477b9eaa3792d</t>
+          <t>https://www.indeed.com/viewjob?jk=6e80fc4f1c8a9728</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Analyst / Engineer</t>
+          <t>Software Engineer II (Python/Java/AWS/Pyspark)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Star Schema, CI/CD, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fb24a781dd0a7af</t>
+          <t>https://www.indeed.com/viewjob?jk=ee9a97ffa509cdb3</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git, Datadog</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=099ab57136f08627</t>
+          <t>https://www.indeed.com/viewjob?jk=fb76cbe4b5a98afe</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DERMS Data Architect &amp; Integration</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GE Vernova</t>
+          <t>Axogen</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Fact Tables, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=381bad2f60317342</t>
+          <t>https://www.indeed.com/viewjob?jk=24d477b9eaa3792d</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Analyst / Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=935ece4128fe6f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=9fb24a781dd0a7af</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II - Encore Program</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0047e52c4d67e20</t>
+          <t>https://www.indeed.com/viewjob?jk=099ab57136f08627</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II - Encore Program</t>
+          <t>DERMS Data Architect &amp; Integration</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GE Vernova</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b91b81ba111bb33b</t>
+          <t>https://www.indeed.com/viewjob?jk=381bad2f60317342</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II - Encore Program</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7afb773581c3b4c0</t>
+          <t>https://www.indeed.com/viewjob?jk=935ece4128fe6f9f</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II - Encore Program</t>
+          <t>Business Informatics Support Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Trillium Health Resources</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95650589278c6f55</t>
+          <t>https://www.indeed.com/viewjob?jk=c1bc5a017b98965e</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II - Encore Program</t>
+          <t>Business Informatics Support Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Trillium Health Resources</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2f93e37daf3e792</t>
+          <t>https://www.indeed.com/viewjob?jk=61b3b18503d4acec</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Business Informatics Support Data Engineer</t>
+          <t>Data Engineer III - (Pyspark/databricks/Mongo/Sql/Python)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Trillium Health Resources</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
+          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,19 +3296,19 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1bc5a017b98965e</t>
+          <t>https://www.indeed.com/viewjob?jk=820ae5b00199f1e8</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Business Informatics Support Data Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Trillium Health Resources</t>
+          <t>Great Gray Trust Company</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, Docker, SonarQube, Git, Python</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61b3b18503d4acec</t>
+          <t>https://www.indeed.com/viewjob?jk=6d12b3ac28ec908f</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer III - (Pyspark/databricks/Mongo/Sql/Python)</t>
+          <t>Software Engineer – Full Stack</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Empower Pharmacy</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=820ae5b00199f1e8</t>
+          <t>https://www.indeed.com/viewjob?jk=e06173fc3c6ce8f8</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineer – Full Stack</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Empower Pharmacy</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06173fc3c6ce8f8</t>
+          <t>https://www.indeed.com/viewjob?jk=e0047e52c4d67e20</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Great Gray Trust Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, Docker, SonarQube, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,7 +3436,112 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d12b3ac28ec908f</t>
+          <t>https://www.indeed.com/viewjob?jk=b91b81ba111bb33b</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer II - Encore Program</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7afb773581c3b4c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer II - Encore Program</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Hermitage, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=95650589278c6f55</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer II - Encore Program</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2f93e37daf3e792</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-25.xlsx
+++ b/results/job_matches_2026-07-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer- Analytics Products</t>
+          <t>Cactus Wellhead - Data Engineer &amp; Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DC PUBLIC CHARTER SCHOOL BOARD</t>
+          <t>Cactus Wellhead</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6722d6963193ac95</t>
+          <t>https://www.indeed.com/viewjob?jk=35a580479028c129</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Platform Engineer VI - Data Services</t>
+          <t>Data Engineer- Analytics Products</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>DC PUBLIC CHARTER SCHOOL BOARD</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=530025f520e267c1</t>
+          <t>https://www.indeed.com/viewjob?jk=6722d6963193ac95</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Platform Engineer VI - Data Services</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TAIT</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lititz, PA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54cfb968de0a9abd</t>
+          <t>https://www.indeed.com/viewjob?jk=530025f520e267c1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data engineer (Power BI)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>TAIT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Lititz, PA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Snowflake, Oracle</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1c4bb478a10661f</t>
+          <t>https://www.indeed.com/viewjob?jk=54cfb968de0a9abd</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data engineer (Power BI)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pyx Health</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,19 +986,19 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea50071b5800db9</t>
+          <t>https://www.indeed.com/viewjob?jk=b1c4bb478a10661f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Pyx Health</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1007,11 +1007,11 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d24836d15aa901f</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea50071b5800db9</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Scientist Senior Associate</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, RDS, Spark, PySpark, Oracle, ETL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c02b7e5e2ede6f3</t>
+          <t>https://www.indeed.com/viewjob?jk=6d24836d15aa901f</t>
         </is>
       </c>
     </row>
@@ -1098,35 +1098,35 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Data Scientist Senior Associate</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Versa Networks</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, GCP, Cloud Storage, Spark, Scala, Dask, Data Modeling, CI/CD, Terraform, Docker</t>
+          <t>AWS, Glue, ECS, RDS, Spark, PySpark, Oracle, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6cd7a40acf5c8ea</t>
+          <t>https://www.indeed.com/viewjob?jk=8c02b7e5e2ede6f3</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Dask, Polars, MLOps, MLflow, Terraform</t>
+          <t>RDS, GCP, Cloud Storage, Spark, Scala, Dask, Data Modeling, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d8fd3bb26a1e48b</t>
+          <t>https://www.indeed.com/viewjob?jk=f6cd7a40acf5c8ea</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Versa Networks</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,17 +1186,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Dask, Polars, MLOps, MLflow, Terraform</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=630d48996f1eac48</t>
+          <t>https://www.indeed.com/viewjob?jk=6d8fd3bb26a1e48b</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7a92b5805d6137</t>
+          <t>https://www.indeed.com/viewjob?jk=630d48996f1eac48</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd3e9bf3427fd2d6</t>
+          <t>https://www.indeed.com/viewjob?jk=9d7a92b5805d6137</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ec6e06ec6b6e3fa</t>
+          <t>https://www.indeed.com/viewjob?jk=fd3e9bf3427fd2d6</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14216a18b53ccbd9</t>
+          <t>https://www.indeed.com/viewjob?jk=3ec6e06ec6b6e3fa</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4bf15647e9f22c6</t>
+          <t>https://www.indeed.com/viewjob?jk=14216a18b53ccbd9</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Surescripts</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4bcd6e2a9d67464</t>
+          <t>https://www.indeed.com/viewjob?jk=c4bf15647e9f22c6</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>Surescripts</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d0c84a27d084fd0</t>
+          <t>https://www.indeed.com/viewjob?jk=d4bcd6e2a9d67464</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>First Citizens Bank</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ac40ad9509eb3e</t>
+          <t>https://www.indeed.com/viewjob?jk=8d0c84a27d084fd0</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior IT Developer TDS (US)</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Kafka, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ba9067ff8ad3678</t>
+          <t>https://www.indeed.com/viewjob?jk=8e283e1b09898d08</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>Senior Analytics Engineer (33139)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e283e1b09898d08</t>
+          <t>https://www.indeed.com/viewjob?jk=9f6d6b581aa01dfb</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (33139)</t>
+          <t>Senior MarTech Engineer (Braze/Claude)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f6d6b581aa01dfb</t>
+          <t>https://www.indeed.com/viewjob?jk=da2cd5f2d2247bd7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior MarTech Engineer (Braze/Claude)</t>
+          <t>Senior IT Developer TDS (US)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,17 +1606,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Kafka, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da2cd5f2d2247bd7</t>
+          <t>https://www.indeed.com/viewjob?jk=4ba9067ff8ad3678</t>
         </is>
       </c>
     </row>
@@ -2008,17 +2008,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>One Call</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=454dc6c270b9d674</t>
+          <t>https://www.indeed.com/viewjob?jk=13f9bc74bc5d1d66</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Sally Beauty</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
+          <t>RDS, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13f9bc74bc5d1d66</t>
+          <t>https://www.indeed.com/viewjob?jk=5832467cbe11eede</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II-Python/PySpark</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Sally Beauty</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5832467cbe11eede</t>
+          <t>https://www.indeed.com/viewjob?jk=bbbc18e6ff889804</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer II-Python/PySpark</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
+          <t>AWS, S3, ECS, IAM, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbbc18e6ff889804</t>
+          <t>https://www.indeed.com/viewjob?jk=76545a7a26014492</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Platform &amp; Integration Engineer (Kafka)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Medica Services Company LLC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76545a7a26014492</t>
+          <t>https://www.indeed.com/viewjob?jk=1a1e479ebfe2163b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Platform &amp; Integration Engineer (Kafka)</t>
+          <t>Senior Platform Engineer (Cloud &amp; AI Platform)- Remote within US</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Medica Services Company LLC</t>
+          <t>OEConnection</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a1e479ebfe2163b</t>
+          <t>https://www.indeed.com/viewjob?jk=024ce94c4237b353</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=024ce94c4237b353</t>
+          <t>https://www.indeed.com/viewjob?jk=e08d2c63dac884c6</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Cloud &amp; AI Platform)- Remote within US</t>
+          <t>Clinical Data Engineer (Application Engineer)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>OEConnection</t>
+          <t>Oregon Health &amp; Science University</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Medallion Architecture, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e08d2c63dac884c6</t>
+          <t>https://www.indeed.com/viewjob?jk=4baa56a62cb41945</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Clinical Data Engineer (Application Engineer)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Oregon Health &amp; Science University</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Azure, Medallion Architecture, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL, Azure DevOps, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4baa56a62cb41945</t>
+          <t>https://www.indeed.com/viewjob?jk=096cfd68dbda7a1a</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Java Developer with AI Experience</t>
+          <t>Senior Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Glint Tech Solutions</t>
+          <t>Ingram Micro</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1f24944a225af1c</t>
+          <t>https://www.indeed.com/viewjob?jk=1fbe4faecbcb6e49</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AWS &amp; Databricks Platform Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=096cfd68dbda7a1a</t>
+          <t>https://www.indeed.com/viewjob?jk=54ffcf229826c509</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Agentic AI Engineer</t>
+          <t>Senior Java Developer with AI Experience</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ingram Micro</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Dask, CI/CD, Git</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fbe4faecbcb6e49</t>
+          <t>https://www.indeed.com/viewjob?jk=c1f24944a225af1c</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AWS &amp; Databricks Platform Architect</t>
+          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Simpson Strong-Tie</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54ffcf229826c509</t>
+          <t>https://www.indeed.com/viewjob?jk=b066ce08bf22f47c</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
+          <t>Artificial Intelligence Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Simpson Strong-Tie</t>
+          <t>M2S Group</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Highland Park, IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b066ce08bf22f47c</t>
+          <t>https://www.indeed.com/viewjob?jk=dde1cd623d007554</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Architect</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>M2S Group</t>
+          <t>BGE, Inc</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Highland Park, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dde1cd623d007554</t>
+          <t>https://www.indeed.com/viewjob?jk=54c4f37450aa9007</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c4f37450aa9007</t>
+          <t>https://www.indeed.com/viewjob?jk=1ed66eb1c43b3061</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ed66eb1c43b3061</t>
+          <t>https://www.indeed.com/viewjob?jk=b4f5eb1da717e31e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BGE, Inc</t>
+          <t>PURE Insurance</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>White Plains, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, ECS, RDS, Databricks, Scala, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4f5eb1da717e31e</t>
+          <t>https://www.indeed.com/viewjob?jk=2b7ea8b8e5406480</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Pre-Sales Solution Architect</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PURE Insurance</t>
+          <t>Blue Orange Digital</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>White Plains, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, Scala, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Snowflake, ELT, dbt</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b7ea8b8e5406480</t>
+          <t>https://www.indeed.com/viewjob?jk=148c58d976f8aa98</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Business Systems Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Frank Darling</t>
+          <t>Precisely</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, DynamoDB, ETL</t>
+          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,19 +2701,19 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d75b0168c3af177d</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3498d244cd3dd0</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Pre-Sales Solution Architect</t>
+          <t>Java AWS Software Engineer III</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Blue Orange Digital</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Snowflake, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=148c58d976f8aa98</t>
+          <t>https://www.indeed.com/viewjob?jk=7e88dcde57fa9ced</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer III - Full Stack ReactJS, Java, Python, AWS + Monday.com Platform</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Databricks, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Scala, SQL Server, MySQL, ETL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e21285074de6c55</t>
+          <t>https://www.indeed.com/viewjob?jk=77de33f1323a932a</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Precisely</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, SQL Server, MySQL, ETL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,67 +2806,67 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3498d244cd3dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=fca0033255b9f7dc</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Java AWS Software Engineer III</t>
+          <t>Data DevOps Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Versa Networks</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, Jenkins, Terraform, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e88dcde57fa9ced</t>
+          <t>https://www.indeed.com/viewjob?jk=6e80fc4f1c8a9728</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Software Engineer II (Python/Java/AWS/Pyspark)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, MySQL, ETL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Star Schema, CI/CD, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77de33f1323a932a</t>
+          <t>https://www.indeed.com/viewjob?jk=ee9a97ffa509cdb3</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, MySQL, ETL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git, Datadog</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fca0033255b9f7dc</t>
+          <t>https://www.indeed.com/viewjob?jk=fb76cbe4b5a98afe</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data DevOps Engineer</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Versa Networks</t>
+          <t>Axogen</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, Jenkins, Terraform, Jenkins, Git, Python</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Fact Tables, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e80fc4f1c8a9728</t>
+          <t>https://www.indeed.com/viewjob?jk=24d477b9eaa3792d</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer II (Python/Java/AWS/Pyspark)</t>
+          <t>Data Analyst / Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Star Schema, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee9a97ffa509cdb3</t>
+          <t>https://www.indeed.com/viewjob?jk=9fb24a781dd0a7af</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Alameda, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git, Datadog</t>
+          <t>RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb76cbe4b5a98afe</t>
+          <t>https://www.indeed.com/viewjob?jk=099ab57136f08627</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>DERMS Data Architect &amp; Integration</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Axogen</t>
+          <t>GE Vernova</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Fact Tables, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24d477b9eaa3792d</t>
+          <t>https://www.indeed.com/viewjob?jk=381bad2f60317342</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Analyst / Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fb24a781dd0a7af</t>
+          <t>https://www.indeed.com/viewjob?jk=935ece4128fe6f9f</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Business Informatics Support Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>Trillium Health Resources</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=099ab57136f08627</t>
+          <t>https://www.indeed.com/viewjob?jk=c1bc5a017b98965e</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DERMS Data Architect &amp; Integration</t>
+          <t>Business Informatics Support Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>GE Vernova</t>
+          <t>Trillium Health Resources</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=381bad2f60317342</t>
+          <t>https://www.indeed.com/viewjob?jk=61b3b18503d4acec</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Engineer III - (Pyspark/databricks/Mongo/Sql/Python)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, Git</t>
+          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=935ece4128fe6f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=820ae5b00199f1e8</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Business Informatics Support Data Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Trillium Health Resources</t>
+          <t>Great Gray Trust Company</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, Docker, SonarQube, Git, Python</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1bc5a017b98965e</t>
+          <t>https://www.indeed.com/viewjob?jk=6d12b3ac28ec908f</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Business Informatics Support Data Engineer</t>
+          <t>Software Engineer – Full Stack</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Trillium Health Resources</t>
+          <t>Empower Pharmacy</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61b3b18503d4acec</t>
+          <t>https://www.indeed.com/viewjob?jk=e06173fc3c6ce8f8</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer III - (Pyspark/databricks/Mongo/Sql/Python)</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=820ae5b00199f1e8</t>
+          <t>https://www.indeed.com/viewjob?jk=e0047e52c4d67e20</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Great Gray Trust Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, Docker, SonarQube, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d12b3ac28ec908f</t>
+          <t>https://www.indeed.com/viewjob?jk=b91b81ba111bb33b</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Engineer – Full Stack</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Empower Pharmacy</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06173fc3c6ce8f8</t>
+          <t>https://www.indeed.com/viewjob?jk=7afb773581c3b4c0</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0047e52c4d67e20</t>
+          <t>https://www.indeed.com/viewjob?jk=95650589278c6f55</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3435,111 +3435,6 @@
         </is>
       </c>
       <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b91b81ba111bb33b</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II - Encore Program</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7afb773581c3b4c0</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II - Encore Program</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Hermitage, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=95650589278c6f55</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II - Encore Program</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=e2f93e37daf3e792</t>
         </is>

--- a/results/job_matches_2026-07-25.xlsx
+++ b/results/job_matches_2026-07-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2253,17 +2253,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Clinical Data Engineer (Application Engineer)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Oregon Health &amp; Science University</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Azure, Medallion Architecture, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL, Azure DevOps, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4baa56a62cb41945</t>
+          <t>https://www.indeed.com/viewjob?jk=096cfd68dbda7a1a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>Ingram Micro</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=096cfd68dbda7a1a</t>
+          <t>https://www.indeed.com/viewjob?jk=1fbe4faecbcb6e49</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Agentic AI Engineer</t>
+          <t>AWS &amp; Databricks Platform Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ingram Micro</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Dask, CI/CD, Git</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fbe4faecbcb6e49</t>
+          <t>https://www.indeed.com/viewjob?jk=54ffcf229826c509</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AWS &amp; Databricks Platform Architect</t>
+          <t>Senior Java Developer with AI Experience</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54ffcf229826c509</t>
+          <t>https://www.indeed.com/viewjob?jk=c1f24944a225af1c</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Java Developer with AI Experience</t>
+          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Glint Tech Solutions</t>
+          <t>Simpson Strong-Tie</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1f24944a225af1c</t>
+          <t>https://www.indeed.com/viewjob?jk=b066ce08bf22f47c</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
+          <t>Artificial Intelligence Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Simpson Strong-Tie</t>
+          <t>M2S Group</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Highland Park, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b066ce08bf22f47c</t>
+          <t>https://www.indeed.com/viewjob?jk=dde1cd623d007554</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Architect</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>M2S Group</t>
+          <t>BGE, Inc</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Highland Park, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dde1cd623d007554</t>
+          <t>https://www.indeed.com/viewjob?jk=54c4f37450aa9007</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c4f37450aa9007</t>
+          <t>https://www.indeed.com/viewjob?jk=1ed66eb1c43b3061</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ed66eb1c43b3061</t>
+          <t>https://www.indeed.com/viewjob?jk=b4f5eb1da717e31e</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BGE, Inc</t>
+          <t>PURE Insurance</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>White Plains, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, ECS, RDS, Databricks, Scala, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4f5eb1da717e31e</t>
+          <t>https://www.indeed.com/viewjob?jk=2b7ea8b8e5406480</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Pre-Sales Solution Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PURE Insurance</t>
+          <t>Blue Orange Digital</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>White Plains, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, Scala, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Snowflake, ELT, dbt</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b7ea8b8e5406480</t>
+          <t>https://www.indeed.com/viewjob?jk=148c58d976f8aa98</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Pre-Sales Solution Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Blue Orange Digital</t>
+          <t>Precisely</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Snowflake, ELT, dbt</t>
+          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=148c58d976f8aa98</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3498d244cd3dd0</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Java AWS Software Engineer III</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Precisely</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3498d244cd3dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=7e88dcde57fa9ced</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Java AWS Software Engineer III</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, Azure, Scala, SQL Server, MySQL, ETL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e88dcde57fa9ced</t>
+          <t>https://www.indeed.com/viewjob?jk=77de33f1323a932a</t>
         </is>
       </c>
     </row>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2771,59 +2771,59 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77de33f1323a932a</t>
+          <t>https://www.indeed.com/viewjob?jk=fca0033255b9f7dc</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Data DevOps Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Versa Networks</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, MySQL, ETL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, Jenkins, Terraform, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fca0033255b9f7dc</t>
+          <t>https://www.indeed.com/viewjob?jk=6e80fc4f1c8a9728</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data DevOps Engineer</t>
+          <t>Software Engineer II (Python/Java/AWS/Pyspark)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Versa Networks</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, Jenkins, Terraform, Jenkins, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Star Schema, CI/CD, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e80fc4f1c8a9728</t>
+          <t>https://www.indeed.com/viewjob?jk=ee9a97ffa509cdb3</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer II (Python/Java/AWS/Pyspark)</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Star Schema, CI/CD, Git</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git, Datadog</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee9a97ffa509cdb3</t>
+          <t>https://www.indeed.com/viewjob?jk=fb76cbe4b5a98afe</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Axogen</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Alameda, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git, Datadog</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Fact Tables, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb76cbe4b5a98afe</t>
+          <t>https://www.indeed.com/viewjob?jk=24d477b9eaa3792d</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Data Analyst / Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Axogen</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Fact Tables, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24d477b9eaa3792d</t>
+          <t>https://www.indeed.com/viewjob?jk=9fb24a781dd0a7af</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Analyst / Engineer</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fb24a781dd0a7af</t>
+          <t>https://www.indeed.com/viewjob?jk=099ab57136f08627</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>DERMS Data Architect &amp; Integration</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>GE Vernova</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=099ab57136f08627</t>
+          <t>https://www.indeed.com/viewjob?jk=381bad2f60317342</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DERMS Data Architect &amp; Integration</t>
+          <t>Business Informatics Support Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GE Vernova</t>
+          <t>Trillium Health Resources</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=381bad2f60317342</t>
+          <t>https://www.indeed.com/viewjob?jk=c1bc5a017b98965e</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Business Informatics Support Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Trillium Health Resources</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=935ece4128fe6f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=61b3b18503d4acec</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Business Informatics Support Data Engineer</t>
+          <t>Data Engineer III - (Pyspark/databricks/Mongo/Sql/Python)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Trillium Health Resources</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
+          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1bc5a017b98965e</t>
+          <t>https://www.indeed.com/viewjob?jk=820ae5b00199f1e8</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Business Informatics Support Data Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Trillium Health Resources</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61b3b18503d4acec</t>
+          <t>https://www.indeed.com/viewjob?jk=935ece4128fe6f9f</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer III - (Pyspark/databricks/Mongo/Sql/Python)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Great Gray Trust Company</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, Docker, SonarQube, Git, Python</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=820ae5b00199f1e8</t>
+          <t>https://www.indeed.com/viewjob?jk=6d12b3ac28ec908f</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer – Full Stack</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Great Gray Trust Company</t>
+          <t>Empower Pharmacy</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, Docker, SonarQube, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d12b3ac28ec908f</t>
+          <t>https://www.indeed.com/viewjob?jk=e06173fc3c6ce8f8</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer – Full Stack</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Empower Pharmacy</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06173fc3c6ce8f8</t>
+          <t>https://www.indeed.com/viewjob?jk=e0047e52c4d67e20</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0047e52c4d67e20</t>
+          <t>https://www.indeed.com/viewjob?jk=b91b81ba111bb33b</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b91b81ba111bb33b</t>
+          <t>https://www.indeed.com/viewjob?jk=7afb773581c3b4c0</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7afb773581c3b4c0</t>
+          <t>https://www.indeed.com/viewjob?jk=95650589278c6f55</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3400,41 +3400,6 @@
         </is>
       </c>
       <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=95650589278c6f55</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II - Encore Program</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=e2f93e37daf3e792</t>
         </is>

--- a/results/job_matches_2026-07-25.xlsx
+++ b/results/job_matches_2026-07-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,25 +573,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer for Patient Safety Measure Engine</t>
+          <t>DevOps Engineer Live Streaming- Wixom, MI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>J&amp;B Medical</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Wixom, MI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d3f3d22744f5363</t>
+          <t>https://www.indeed.com/viewjob?jk=41ea01c619cf5f4e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DevOps Engineer Live Streaming- Wixom, MI</t>
+          <t>Sr. Engineer, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>J&amp;B Medical</t>
+          <t>Lovesac</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Wixom, MI, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP, Scala</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Medallion Architecture, BigQuery, Dataflow, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41ea01c619cf5f4e</t>
+          <t>https://www.indeed.com/viewjob?jk=2d666b2674d51e46</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Data &amp; Analytics</t>
+          <t>AWS Cloud Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lovesac</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Medallion Architecture, BigQuery, Dataflow, Spark, PySpark</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d666b2674d51e46</t>
+          <t>https://www.indeed.com/viewjob?jk=e3a616293a442292</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AWS Cloud Architect</t>
+          <t>Senior DataOps Engineer ( Remote US)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cloud and Things</t>
+          <t>Smile Digital Health</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, Splunk, CI/CD</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Spark, Scala, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,19 +706,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3a616293a442292</t>
+          <t>https://www.indeed.com/viewjob?jk=b9cf29eaf2fb3e62</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior DataOps Engineer ( Remote US)</t>
+          <t>Senior Data Engineer (33142)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Smile Digital Health</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -731,69 +731,69 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Spark, Scala, DataOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9cf29eaf2fb3e62</t>
+          <t>https://www.indeed.com/viewjob?jk=614b737b604716f8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (33142)</t>
+          <t>Cactus Wellhead - Data Engineer &amp; Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>Cactus Wellhead</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=614b737b604716f8</t>
+          <t>https://www.indeed.com/viewjob?jk=35a580479028c129</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Engineer- Analytics Products</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Gradera</t>
+          <t>DC PUBLIC CHARTER SCHOOL BOARD</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f26c60aecfc298d</t>
+          <t>https://www.indeed.com/viewjob?jk=6722d6963193ac95</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cactus Wellhead - Data Engineer &amp; Architect</t>
+          <t>Platform Engineer VI - Data Services</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cactus Wellhead</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35a580479028c129</t>
+          <t>https://www.indeed.com/viewjob?jk=530025f520e267c1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer- Analytics Products</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DC PUBLIC CHARTER SCHOOL BOARD</t>
+          <t>Gradera</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6722d6963193ac95</t>
+          <t>https://www.indeed.com/viewjob?jk=0f26c60aecfc298d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Platform Engineer VI - Data Services</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>TAIT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Lititz, PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=530025f520e267c1</t>
+          <t>https://www.indeed.com/viewjob?jk=54cfb968de0a9abd</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data engineer (Power BI)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TAIT</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lititz, PA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54cfb968de0a9abd</t>
+          <t>https://www.indeed.com/viewjob?jk=b1c4bb478a10661f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data engineer (Power BI)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Pyx Health</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Snowflake, Oracle</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,19 +986,19 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1c4bb478a10661f</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea50071b5800db9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pyx Health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1007,11 +1007,11 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea50071b5800db9</t>
+          <t>https://www.indeed.com/viewjob?jk=6d24836d15aa901f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Data Scientist Senior Associate</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, ECS, RDS, Spark, PySpark, Oracle, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d24836d15aa901f</t>
+          <t>https://www.indeed.com/viewjob?jk=8c02b7e5e2ede6f3</t>
         </is>
       </c>
     </row>
@@ -1098,52 +1098,52 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Scientist Senior Associate</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Versa Networks</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, RDS, Spark, PySpark, Oracle, ETL, Splunk, CI/CD</t>
+          <t>RDS, GCP, Cloud Storage, Spark, Scala, Dask, Data Modeling, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c02b7e5e2ede6f3</t>
+          <t>https://www.indeed.com/viewjob?jk=f6cd7a40acf5c8ea</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Versa Networks</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, GCP, Cloud Storage, Spark, Scala, Dask, Data Modeling, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6cd7a40acf5c8ea</t>
+          <t>https://www.indeed.com/viewjob?jk=630d48996f1eac48</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Versa Networks</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,17 +1186,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Dask, Polars, MLOps, MLflow, Terraform</t>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d8fd3bb26a1e48b</t>
+          <t>https://www.indeed.com/viewjob?jk=9d7a92b5805d6137</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=630d48996f1eac48</t>
+          <t>https://www.indeed.com/viewjob?jk=fd3e9bf3427fd2d6</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7a92b5805d6137</t>
+          <t>https://www.indeed.com/viewjob?jk=3ec6e06ec6b6e3fa</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd3e9bf3427fd2d6</t>
+          <t>https://www.indeed.com/viewjob?jk=14216a18b53ccbd9</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ec6e06ec6b6e3fa</t>
+          <t>https://www.indeed.com/viewjob?jk=c4bf15647e9f22c6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Surescripts</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14216a18b53ccbd9</t>
+          <t>https://www.indeed.com/viewjob?jk=d4bcd6e2a9d67464</t>
         </is>
       </c>
     </row>
@@ -1383,12 +1383,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4bf15647e9f22c6</t>
+          <t>https://www.indeed.com/viewjob?jk=8d0c84a27d084fd0</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Surescripts</t>
+          <t>Versa Networks</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Dask, Polars, MLOps, MLflow, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4bcd6e2a9d67464</t>
+          <t>https://www.indeed.com/viewjob?jk=6d8fd3bb26a1e48b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior IT Developer TDS (US)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Scala, Kafka, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d0c84a27d084fd0</t>
+          <t>https://www.indeed.com/viewjob?jk=4ba9067ff8ad3678</t>
         </is>
       </c>
     </row>
@@ -1588,17 +1588,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior IT Developer TDS (US)</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Kafka, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ba9067ff8ad3678</t>
+          <t>https://www.indeed.com/viewjob?jk=3949515f70fcddc9</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Senior Systems Engineer - Delivery DevOps</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, BigQuery, Scala, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3949515f70fcddc9</t>
+          <t>https://www.indeed.com/viewjob?jk=7f60289bd7b154e2</t>
         </is>
       </c>
     </row>
@@ -1728,17 +1728,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer - Delivery DevOps</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,42 +1756,42 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f60289bd7b154e2</t>
+          <t>https://www.indeed.com/viewjob?jk=a0600fe838e8fd40</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Sr. Software Engineer, Cloud - Analytics Platform</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, ECS, RDS, Spark, Scala, MySQL, DynamoDB, Cassandra, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0600fe838e8fd40</t>
+          <t>https://www.indeed.com/viewjob?jk=ec75113b2386de94</t>
         </is>
       </c>
     </row>
@@ -1833,17 +1833,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Cloud - Analytics Platform</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,42 +1851,42 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Spark, Scala, MySQL, DynamoDB, Cassandra, NoSQL, Jenkins</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec75113b2386de94</t>
+          <t>https://www.indeed.com/viewjob?jk=1b73563a16146db3</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Liquidity Services, Inc.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Redshift, Azure, BigQuery, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b73563a16146db3</t>
+          <t>https://www.indeed.com/viewjob?jk=faf4368f99c56fa7</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Sally Beauty</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Data Modeling, CI/CD</t>
+          <t>RDS, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4beac6cc3645a53b</t>
+          <t>https://www.indeed.com/viewjob?jk=5832467cbe11eede</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II-Python/PySpark</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Liquidity Services, Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, BigQuery, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf4368f99c56fa7</t>
+          <t>https://www.indeed.com/viewjob?jk=bbbc18e6ff889804</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>AWS, S3, ECS, IAM, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcc108d020014d64</t>
+          <t>https://www.indeed.com/viewjob?jk=76545a7a26014492</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13f9bc74bc5d1d66</t>
+          <t>https://www.indeed.com/viewjob?jk=fcc108d020014d64</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Platform &amp; Integration Engineer (Kafka)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Sally Beauty</t>
+          <t>Medica Services Company LLC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5832467cbe11eede</t>
+          <t>https://www.indeed.com/viewjob?jk=1a1e479ebfe2163b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer II-Python/PySpark</t>
+          <t>Senior Platform Engineer (Cloud &amp; AI Platform)- Remote within US</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>OEConnection</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbbc18e6ff889804</t>
+          <t>https://www.indeed.com/viewjob?jk=024ce94c4237b353</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Platform Engineer (Cloud &amp; AI Platform)- Remote within US</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>OEConnection</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76545a7a26014492</t>
+          <t>https://www.indeed.com/viewjob?jk=e08d2c63dac884c6</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Platform &amp; Integration Engineer (Kafka)</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Medica Services Company LLC</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a1e479ebfe2163b</t>
+          <t>https://www.indeed.com/viewjob?jk=13f9bc74bc5d1d66</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Cloud &amp; AI Platform)- Remote within US</t>
+          <t>Senior Java Developer with AI Experience</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>OEConnection</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=024ce94c4237b353</t>
+          <t>https://www.indeed.com/viewjob?jk=c1f24944a225af1c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Cloud &amp; AI Platform)- Remote within US</t>
+          <t>Senior Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>OEConnection</t>
+          <t>Ingram Micro</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e08d2c63dac884c6</t>
+          <t>https://www.indeed.com/viewjob?jk=1fbe4faecbcb6e49</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AWS &amp; Databricks Platform Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=096cfd68dbda7a1a</t>
+          <t>https://www.indeed.com/viewjob?jk=54ffcf229826c509</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Agentic AI Engineer</t>
+          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ingram Micro</t>
+          <t>Simpson Strong-Tie</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Dask, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fbe4faecbcb6e49</t>
+          <t>https://www.indeed.com/viewjob?jk=b066ce08bf22f47c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AWS &amp; Databricks Platform Architect</t>
+          <t>Artificial Intelligence Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>M2S Group</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Highland Park, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54ffcf229826c509</t>
+          <t>https://www.indeed.com/viewjob?jk=dde1cd623d007554</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Java Developer with AI Experience</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Glint Tech Solutions</t>
+          <t>BGE, Inc</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1f24944a225af1c</t>
+          <t>https://www.indeed.com/viewjob?jk=54c4f37450aa9007</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Simpson Strong-Tie</t>
+          <t>BGE, Inc</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b066ce08bf22f47c</t>
+          <t>https://www.indeed.com/viewjob?jk=1ed66eb1c43b3061</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Architect</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>M2S Group</t>
+          <t>BGE, Inc</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Highland Park, IL, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dde1cd623d007554</t>
+          <t>https://www.indeed.com/viewjob?jk=b4f5eb1da717e31e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Pre-Sales Solution Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BGE, Inc</t>
+          <t>Blue Orange Digital</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Snowflake, ELT, dbt</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c4f37450aa9007</t>
+          <t>https://www.indeed.com/viewjob?jk=148c58d976f8aa98</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BGE, Inc</t>
+          <t>PURE Insurance</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>White Plains, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, ECS, RDS, Databricks, Scala, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ed66eb1c43b3061</t>
+          <t>https://www.indeed.com/viewjob?jk=2b7ea8b8e5406480</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BGE, Inc</t>
+          <t>Precisely</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4f5eb1da717e31e</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3498d244cd3dd0</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Java AWS Software Engineer III</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PURE Insurance</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>White Plains, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, Scala, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b7ea8b8e5406480</t>
+          <t>https://www.indeed.com/viewjob?jk=7e88dcde57fa9ced</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Pre-Sales Solution Architect</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Blue Orange Digital</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Snowflake, ELT, dbt</t>
+          <t>AWS, Azure, Scala, SQL Server, MySQL, ETL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=148c58d976f8aa98</t>
+          <t>https://www.indeed.com/viewjob?jk=77de33f1323a932a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Precisely</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, SQL Server, MySQL, ETL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,67 +2666,67 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3498d244cd3dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=fca0033255b9f7dc</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Java AWS Software Engineer III</t>
+          <t>Data DevOps Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Versa Networks</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, Jenkins, Terraform, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e88dcde57fa9ced</t>
+          <t>https://www.indeed.com/viewjob?jk=6e80fc4f1c8a9728</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, MySQL, ETL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git, Datadog</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77de33f1323a932a</t>
+          <t>https://www.indeed.com/viewjob?jk=fb76cbe4b5a98afe</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Software Engineer II (Python/Java/AWS/Pyspark)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, MySQL, ETL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Star Schema, CI/CD, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fca0033255b9f7dc</t>
+          <t>https://www.indeed.com/viewjob?jk=ee9a97ffa509cdb3</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data DevOps Engineer</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Versa Networks</t>
+          <t>Axogen</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, Jenkins, Terraform, Jenkins, Git, Python</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Fact Tables, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e80fc4f1c8a9728</t>
+          <t>https://www.indeed.com/viewjob?jk=24d477b9eaa3792d</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer II (Python/Java/AWS/Pyspark)</t>
+          <t>Data Analyst / Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Star Schema, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee9a97ffa509cdb3</t>
+          <t>https://www.indeed.com/viewjob?jk=9fb24a781dd0a7af</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Alameda, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git, Datadog</t>
+          <t>RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb76cbe4b5a98afe</t>
+          <t>https://www.indeed.com/viewjob?jk=099ab57136f08627</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>DERMS Data Architect &amp; Integration</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Axogen</t>
+          <t>GE Vernova</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Fact Tables, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24d477b9eaa3792d</t>
+          <t>https://www.indeed.com/viewjob?jk=381bad2f60317342</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Analyst / Engineer</t>
+          <t>Business Informatics Support Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Trillium Health Resources</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fb24a781dd0a7af</t>
+          <t>https://www.indeed.com/viewjob?jk=c1bc5a017b98965e</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Business Informatics Support Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>Trillium Health Resources</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=099ab57136f08627</t>
+          <t>https://www.indeed.com/viewjob?jk=61b3b18503d4acec</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>DERMS Data Architect &amp; Integration</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GE Vernova</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=381bad2f60317342</t>
+          <t>https://www.indeed.com/viewjob?jk=935ece4128fe6f9f</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Business Informatics Support Data Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Trillium Health Resources</t>
+          <t>Great Gray Trust Company</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, Docker, SonarQube, Git, Python</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1bc5a017b98965e</t>
+          <t>https://www.indeed.com/viewjob?jk=6d12b3ac28ec908f</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Business Informatics Support Data Engineer</t>
+          <t>Software Engineer – Full Stack</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Trillium Health Resources</t>
+          <t>Empower Pharmacy</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61b3b18503d4acec</t>
+          <t>https://www.indeed.com/viewjob?jk=e06173fc3c6ce8f8</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer III - (Pyspark/databricks/Mongo/Sql/Python)</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=820ae5b00199f1e8</t>
+          <t>https://www.indeed.com/viewjob?jk=e0047e52c4d67e20</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=935ece4128fe6f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=b91b81ba111bb33b</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Great Gray Trust Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, Docker, SonarQube, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d12b3ac28ec908f</t>
+          <t>https://www.indeed.com/viewjob?jk=7afb773581c3b4c0</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer – Full Stack</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Empower Pharmacy</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06173fc3c6ce8f8</t>
+          <t>https://www.indeed.com/viewjob?jk=95650589278c6f55</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3260,146 +3260,6 @@
         </is>
       </c>
       <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e0047e52c4d67e20</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II - Encore Program</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b91b81ba111bb33b</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II - Encore Program</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7afb773581c3b4c0</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II - Encore Program</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Hermitage, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=95650589278c6f55</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II - Encore Program</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=e2f93e37daf3e792</t>
         </is>

--- a/results/job_matches_2026-07-25.xlsx
+++ b/results/job_matches_2026-07-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Azure Cloud Architect</t>
+          <t>Software Engineer III-Databricks</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cloud and Things</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, Event Hubs</t>
+          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e5bb3180486d837</t>
+          <t>https://www.indeed.com/viewjob?jk=097f3e8cd3b1164b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer III-Databricks</t>
+          <t>DevOps Engineer Live Streaming- Wixom, MI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>J&amp;B Medical</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Wixom, MI, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=097f3e8cd3b1164b</t>
+          <t>https://www.indeed.com/viewjob?jk=41ea01c619cf5f4e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DevOps Engineer Live Streaming- Wixom, MI</t>
+          <t>Sr. Engineer, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>J&amp;B Medical</t>
+          <t>Lovesac</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wixom, MI, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP, Scala</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Medallion Architecture, BigQuery, Dataflow, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41ea01c619cf5f4e</t>
+          <t>https://www.indeed.com/viewjob?jk=2d666b2674d51e46</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Data &amp; Analytics</t>
+          <t>Senior DataOps Engineer ( Remote US)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lovesac</t>
+          <t>Smile Digital Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Medallion Architecture, BigQuery, Dataflow, Spark, PySpark</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Spark, Scala, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d666b2674d51e46</t>
+          <t>https://www.indeed.com/viewjob?jk=b9cf29eaf2fb3e62</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AWS Cloud Architect</t>
+          <t>Senior Data Engineer (33142)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cloud and Things</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3a616293a442292</t>
+          <t>https://www.indeed.com/viewjob?jk=614b737b604716f8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior DataOps Engineer ( Remote US)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Smile Digital Health</t>
+          <t>Gradera</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Spark, Scala, DataOps, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,59 +706,59 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9cf29eaf2fb3e62</t>
+          <t>https://www.indeed.com/viewjob?jk=0f26c60aecfc298d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (33142)</t>
+          <t>Cactus Wellhead - Data Engineer &amp; Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>Cactus Wellhead</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=614b737b604716f8</t>
+          <t>https://www.indeed.com/viewjob?jk=35a580479028c129</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cactus Wellhead - Data Engineer &amp; Architect</t>
+          <t>Data Engineer- Analytics Products</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cactus Wellhead</t>
+          <t>DC PUBLIC CHARTER SCHOOL BOARD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35a580479028c129</t>
+          <t>https://www.indeed.com/viewjob?jk=6722d6963193ac95</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer- Analytics Products</t>
+          <t>Platform Engineer VI - Data Services</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DC PUBLIC CHARTER SCHOOL BOARD</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6722d6963193ac95</t>
+          <t>https://www.indeed.com/viewjob?jk=530025f520e267c1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Platform Engineer VI - Data Services</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>TAIT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Lititz, PA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=530025f520e267c1</t>
+          <t>https://www.indeed.com/viewjob?jk=54cfb968de0a9abd</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data engineer (Power BI)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Gradera</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f26c60aecfc298d</t>
+          <t>https://www.indeed.com/viewjob?jk=b1c4bb478a10661f</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TAIT</t>
+          <t>Pyx Health</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lititz, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54cfb968de0a9abd</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea50071b5800db9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data engineer (Power BI)</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1c4bb478a10661f</t>
+          <t>https://www.indeed.com/viewjob?jk=6d24836d15aa901f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Scientist Senior Associate</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pyx Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, ECS, RDS, Spark, PySpark, Oracle, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea50071b5800db9</t>
+          <t>https://www.indeed.com/viewjob?jk=8c02b7e5e2ede6f3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>DevOps Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Unlimited Systems</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, SQS, API Gateway, ECS, IAM, RDS, Azure, Scala, Kafka, Splunk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,94 +1021,94 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d24836d15aa901f</t>
+          <t>https://www.indeed.com/viewjob?jk=e19d2be5d242f190</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Scientist Senior Associate</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Versa Networks</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, RDS, Spark, PySpark, Oracle, ETL, Splunk, CI/CD</t>
+          <t>RDS, GCP, Cloud Storage, Spark, Scala, Dask, Data Modeling, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c02b7e5e2ede6f3</t>
+          <t>https://www.indeed.com/viewjob?jk=f6cd7a40acf5c8ea</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Hybrid)</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Unlimited Systems</t>
+          <t>Versa Networks</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, ECS, IAM, RDS, Azure, Scala, Kafka, Splunk</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Dask, Polars, MLOps, MLflow, Terraform</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e19d2be5d242f190</t>
+          <t>https://www.indeed.com/viewjob?jk=6d8fd3bb26a1e48b</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Versa Networks</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,17 +1116,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, GCP, Cloud Storage, Spark, Scala, Dask, Data Modeling, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6cd7a40acf5c8ea</t>
+          <t>https://www.indeed.com/viewjob?jk=630d48996f1eac48</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=630d48996f1eac48</t>
+          <t>https://www.indeed.com/viewjob?jk=9d7a92b5805d6137</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7a92b5805d6137</t>
+          <t>https://www.indeed.com/viewjob?jk=fd3e9bf3427fd2d6</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd3e9bf3427fd2d6</t>
+          <t>https://www.indeed.com/viewjob?jk=3ec6e06ec6b6e3fa</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ec6e06ec6b6e3fa</t>
+          <t>https://www.indeed.com/viewjob?jk=14216a18b53ccbd9</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14216a18b53ccbd9</t>
+          <t>https://www.indeed.com/viewjob?jk=c4bf15647e9f22c6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Surescripts</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4bf15647e9f22c6</t>
+          <t>https://www.indeed.com/viewjob?jk=d4bcd6e2a9d67464</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Senior IT Developer TDS (US)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Surescripts</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, Power BI, Tableau</t>
+          <t>RDS, Azure, Databricks, Scala, Kafka, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4bcd6e2a9d67464</t>
+          <t>https://www.indeed.com/viewjob?jk=4ba9067ff8ad3678</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d0c84a27d084fd0</t>
+          <t>https://www.indeed.com/viewjob?jk=8e283e1b09898d08</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Senior Analytics Engineer (33139)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Versa Networks</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Dask, Polars, MLOps, MLflow, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d8fd3bb26a1e48b</t>
+          <t>https://www.indeed.com/viewjob?jk=9f6d6b581aa01dfb</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior IT Developer TDS (US)</t>
+          <t>Senior MarTech Engineer (Braze/Claude)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Kafka, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ba9067ff8ad3678</t>
+          <t>https://www.indeed.com/viewjob?jk=da2cd5f2d2247bd7</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,102 +1511,102 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e283e1b09898d08</t>
+          <t>https://www.indeed.com/viewjob?jk=3949515f70fcddc9</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (33139)</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f6d6b581aa01dfb</t>
+          <t>https://www.indeed.com/viewjob?jk=ac326e94203a756e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior MarTech Engineer (Braze/Claude)</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da2cd5f2d2247bd7</t>
+          <t>https://www.indeed.com/viewjob?jk=7424c005b9ced1ab</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Senior Systems Engineer - Delivery DevOps</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, BigQuery, Scala, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3949515f70fcddc9</t>
+          <t>https://www.indeed.com/viewjob?jk=7f60289bd7b154e2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer - Delivery DevOps</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f60289bd7b154e2</t>
+          <t>https://www.indeed.com/viewjob?jk=a0600fe838e8fd40</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Software Engineer III - Cloud Data Platform</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac326e94203a756e</t>
+          <t>https://www.indeed.com/viewjob?jk=26ac8e996e1bb5d6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Sr. Software Engineer, Cloud - Analytics Platform</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, MySQL, MongoDB</t>
+          <t>AWS, ECS, RDS, Spark, Scala, MySQL, DynamoDB, Cassandra, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7424c005b9ced1ab</t>
+          <t>https://www.indeed.com/viewjob?jk=ec75113b2386de94</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Associate Cloud &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>First Orion</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>North Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Kinesis, S3, SQS, IAM, RDS, Scala, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0600fe838e8fd40</t>
+          <t>https://www.indeed.com/viewjob?jk=6f4ff182033422db</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Cloud - Analytics Platform</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,42 +1781,42 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Spark, Scala, MySQL, DynamoDB, Cassandra, NoSQL, Jenkins</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec75113b2386de94</t>
+          <t>https://www.indeed.com/viewjob?jk=1b73563a16146db3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer III - Cloud Data Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Liquidity Services, Inc.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, Redshift, Azure, BigQuery, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26ac8e996e1bb5d6</t>
+          <t>https://www.indeed.com/viewjob?jk=faf4368f99c56fa7</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b73563a16146db3</t>
+          <t>https://www.indeed.com/viewjob?jk=fcc108d020014d64</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Liquidity Services, Inc.</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,17 +1886,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, BigQuery, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf4368f99c56fa7</t>
+          <t>https://www.indeed.com/viewjob?jk=13f9bc74bc5d1d66</t>
         </is>
       </c>
     </row>
@@ -2008,17 +2008,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Platform &amp; Integration Engineer (Kafka)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Medica Services Company LLC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcc108d020014d64</t>
+          <t>https://www.indeed.com/viewjob?jk=1a1e479ebfe2163b</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Platform &amp; Integration Engineer (Kafka)</t>
+          <t>Senior Platform Engineer (Cloud &amp; AI Platform)- Remote within US</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Medica Services Company LLC</t>
+          <t>OEConnection</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a1e479ebfe2163b</t>
+          <t>https://www.indeed.com/viewjob?jk=024ce94c4237b353</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=024ce94c4237b353</t>
+          <t>https://www.indeed.com/viewjob?jk=e08d2c63dac884c6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Cloud &amp; AI Platform)- Remote within US</t>
+          <t>AWS &amp; Databricks Platform Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>OEConnection</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e08d2c63dac884c6</t>
+          <t>https://www.indeed.com/viewjob?jk=54ffcf229826c509</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>Senior Java Developer with AI Experience</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13f9bc74bc5d1d66</t>
+          <t>https://www.indeed.com/viewjob?jk=c1f24944a225af1c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Java Developer with AI Experience</t>
+          <t>Senior Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Glint Tech Solutions</t>
+          <t>Ingram Micro</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1f24944a225af1c</t>
+          <t>https://www.indeed.com/viewjob?jk=1fbe4faecbcb6e49</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Agentic AI Engineer</t>
+          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ingram Micro</t>
+          <t>Simpson Strong-Tie</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Dask, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fbe4faecbcb6e49</t>
+          <t>https://www.indeed.com/viewjob?jk=b066ce08bf22f47c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AWS &amp; Databricks Platform Architect</t>
+          <t>Artificial Intelligence Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>M2S Group</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Highland Park, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54ffcf229826c509</t>
+          <t>https://www.indeed.com/viewjob?jk=dde1cd623d007554</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Simpson Strong-Tie</t>
+          <t>BGE, Inc</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b066ce08bf22f47c</t>
+          <t>https://www.indeed.com/viewjob?jk=54c4f37450aa9007</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Architect</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>M2S Group</t>
+          <t>BGE, Inc</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Highland Park, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dde1cd623d007554</t>
+          <t>https://www.indeed.com/viewjob?jk=1ed66eb1c43b3061</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c4f37450aa9007</t>
+          <t>https://www.indeed.com/viewjob?jk=b4f5eb1da717e31e</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Pre-Sales Solution Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BGE, Inc</t>
+          <t>Blue Orange Digital</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Snowflake, ELT, dbt</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ed66eb1c43b3061</t>
+          <t>https://www.indeed.com/viewjob?jk=148c58d976f8aa98</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BGE, Inc</t>
+          <t>PURE Insurance</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>White Plains, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, ECS, RDS, Databricks, Scala, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4f5eb1da717e31e</t>
+          <t>https://www.indeed.com/viewjob?jk=2b7ea8b8e5406480</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Pre-Sales Solution Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Blue Orange Digital</t>
+          <t>Precisely</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Snowflake, ELT, dbt</t>
+          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=148c58d976f8aa98</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3498d244cd3dd0</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Java AWS Software Engineer III</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PURE Insurance</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>White Plains, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, Scala, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b7ea8b8e5406480</t>
+          <t>https://www.indeed.com/viewjob?jk=7e88dcde57fa9ced</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Precisely</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, SQL Server, MySQL, ETL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3498d244cd3dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=77de33f1323a932a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Java AWS Software Engineer III</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, Azure, Scala, SQL Server, MySQL, ETL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,67 +2596,67 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e88dcde57fa9ced</t>
+          <t>https://www.indeed.com/viewjob?jk=fca0033255b9f7dc</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Data DevOps Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>Versa Networks</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, MySQL, ETL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, Jenkins, Terraform, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77de33f1323a932a</t>
+          <t>https://www.indeed.com/viewjob?jk=6e80fc4f1c8a9728</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Software Engineer II (Python/Java/AWS/Pyspark)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, MySQL, ETL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Star Schema, CI/CD, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fca0033255b9f7dc</t>
+          <t>https://www.indeed.com/viewjob?jk=ee9a97ffa509cdb3</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data DevOps Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Versa Networks</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, Jenkins, Terraform, Jenkins, Git, Python</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git, Datadog</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e80fc4f1c8a9728</t>
+          <t>https://www.indeed.com/viewjob?jk=fb76cbe4b5a98afe</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Axogen</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Alameda, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git, Datadog</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Fact Tables, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb76cbe4b5a98afe</t>
+          <t>https://www.indeed.com/viewjob?jk=24d477b9eaa3792d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer II (Python/Java/AWS/Pyspark)</t>
+          <t>Data Analyst / Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Star Schema, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee9a97ffa509cdb3</t>
+          <t>https://www.indeed.com/viewjob?jk=9fb24a781dd0a7af</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Axogen</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Fact Tables, Power BI, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24d477b9eaa3792d</t>
+          <t>https://www.indeed.com/viewjob?jk=099ab57136f08627</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Analyst / Engineer</t>
+          <t>DERMS Data Architect &amp; Integration</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>GE Vernova</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fb24a781dd0a7af</t>
+          <t>https://www.indeed.com/viewjob?jk=381bad2f60317342</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Business Informatics Support Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>Trillium Health Resources</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=099ab57136f08627</t>
+          <t>https://www.indeed.com/viewjob?jk=c1bc5a017b98965e</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>DERMS Data Architect &amp; Integration</t>
+          <t>Business Informatics Support Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GE Vernova</t>
+          <t>Trillium Health Resources</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=381bad2f60317342</t>
+          <t>https://www.indeed.com/viewjob?jk=61b3b18503d4acec</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Business Informatics Support Data Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Trillium Health Resources</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,19 +2946,19 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1bc5a017b98965e</t>
+          <t>https://www.indeed.com/viewjob?jk=935ece4128fe6f9f</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Business Informatics Support Data Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Trillium Health Resources</t>
+          <t>Great Gray Trust Company</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, Docker, SonarQube, Git, Python</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61b3b18503d4acec</t>
+          <t>https://www.indeed.com/viewjob?jk=6d12b3ac28ec908f</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Software Engineer – Full Stack</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Empower Pharmacy</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=935ece4128fe6f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=e06173fc3c6ce8f8</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Great Gray Trust Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, Docker, SonarQube, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d12b3ac28ec908f</t>
+          <t>https://www.indeed.com/viewjob?jk=e0047e52c4d67e20</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer – Full Stack</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Empower Pharmacy</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06173fc3c6ce8f8</t>
+          <t>https://www.indeed.com/viewjob?jk=b91b81ba111bb33b</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0047e52c4d67e20</t>
+          <t>https://www.indeed.com/viewjob?jk=7afb773581c3b4c0</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b91b81ba111bb33b</t>
+          <t>https://www.indeed.com/viewjob?jk=95650589278c6f55</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3190,76 +3190,6 @@
         </is>
       </c>
       <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7afb773581c3b4c0</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II - Encore Program</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Hermitage, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=95650589278c6f55</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II - Encore Program</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=e2f93e37daf3e792</t>
         </is>

--- a/results/job_matches_2026-07-25.xlsx
+++ b/results/job_matches_2026-07-25.xlsx
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Scientist Senior Associate</t>
+          <t>DevOps Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Unlimited Systems</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, RDS, Spark, PySpark, Oracle, ETL, Splunk, CI/CD</t>
+          <t>AWS, SQS, API Gateway, ECS, IAM, RDS, Azure, Scala, Kafka, Splunk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c02b7e5e2ede6f3</t>
+          <t>https://www.indeed.com/viewjob?jk=e19d2be5d242f190</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Hybrid)</t>
+          <t>Data Scientist Senior Associate</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Unlimited Systems</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, ECS, IAM, RDS, Azure, Scala, Kafka, Splunk</t>
+          <t>AWS, Glue, ECS, RDS, Spark, PySpark, Oracle, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e19d2be5d242f190</t>
+          <t>https://www.indeed.com/viewjob?jk=8c02b7e5e2ede6f3</t>
         </is>
       </c>
     </row>
@@ -1308,17 +1308,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Surescripts</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4bcd6e2a9d67464</t>
+          <t>https://www.indeed.com/viewjob?jk=8e283e1b09898d08</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior IT Developer TDS (US)</t>
+          <t>Senior Analytics Engineer (33139)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Kafka, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ba9067ff8ad3678</t>
+          <t>https://www.indeed.com/viewjob?jk=9f6d6b581aa01dfb</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>Senior MarTech Engineer (Braze/Claude)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e283e1b09898d08</t>
+          <t>https://www.indeed.com/viewjob?jk=da2cd5f2d2247bd7</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (33139)</t>
+          <t>Senior IT Developer TDS (US)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Scala, Kafka, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f6d6b581aa01dfb</t>
+          <t>https://www.indeed.com/viewjob?jk=4ba9067ff8ad3678</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior MarTech Engineer (Braze/Claude)</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,42 +1466,42 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da2cd5f2d2247bd7</t>
+          <t>https://www.indeed.com/viewjob?jk=3949515f70fcddc9</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3949515f70fcddc9</t>
+          <t>https://www.indeed.com/viewjob?jk=ac326e94203a756e</t>
         </is>
       </c>
     </row>
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac326e94203a756e</t>
+          <t>https://www.indeed.com/viewjob?jk=7424c005b9ced1ab</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Systems Engineer - Delivery DevOps</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, MySQL, MongoDB</t>
+          <t>AWS, RDS, BigQuery, Scala, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7424c005b9ced1ab</t>
+          <t>https://www.indeed.com/viewjob?jk=7f60289bd7b154e2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer - Delivery DevOps</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f60289bd7b154e2</t>
+          <t>https://www.indeed.com/viewjob?jk=a0600fe838e8fd40</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Software Engineer III - Cloud Data Platform</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0600fe838e8fd40</t>
+          <t>https://www.indeed.com/viewjob?jk=26ac8e996e1bb5d6</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer III - Cloud Data Platform</t>
+          <t>Sr. Software Engineer, Cloud - Analytics Platform</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, ECS, RDS, Spark, Scala, MySQL, DynamoDB, Cassandra, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26ac8e996e1bb5d6</t>
+          <t>https://www.indeed.com/viewjob?jk=ec75113b2386de94</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Cloud - Analytics Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,17 +1711,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Spark, Scala, MySQL, DynamoDB, Cassandra, NoSQL, Jenkins</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec75113b2386de94</t>
+          <t>https://www.indeed.com/viewjob?jk=4bdb09774bada084</t>
         </is>
       </c>
     </row>
@@ -2113,17 +2113,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AWS &amp; Databricks Platform Architect</t>
+          <t>Senior Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Ingram Micro</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54ffcf229826c509</t>
+          <t>https://www.indeed.com/viewjob?jk=1fbe4faecbcb6e49</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Java Developer with AI Experience</t>
+          <t>AWS &amp; Databricks Platform Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Glint Tech Solutions</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1f24944a225af1c</t>
+          <t>https://www.indeed.com/viewjob?jk=54ffcf229826c509</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Agentic AI Engineer</t>
+          <t>Senior Java Developer with AI Experience</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ingram Micro</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Dask, CI/CD, Git</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fbe4faecbcb6e49</t>
+          <t>https://www.indeed.com/viewjob?jk=c1f24944a225af1c</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-25.xlsx
+++ b/results/job_matches_2026-07-25.xlsx
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Cactus Wellhead - Data Engineer &amp; Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Gradera</t>
+          <t>Cactus Wellhead</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f26c60aecfc298d</t>
+          <t>https://www.indeed.com/viewjob?jk=35a580479028c129</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cactus Wellhead - Data Engineer &amp; Architect</t>
+          <t>Data Engineer- Analytics Products</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cactus Wellhead</t>
+          <t>DC PUBLIC CHARTER SCHOOL BOARD</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35a580479028c129</t>
+          <t>https://www.indeed.com/viewjob?jk=6722d6963193ac95</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer- Analytics Products</t>
+          <t>Platform Engineer VI - Data Services</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DC PUBLIC CHARTER SCHOOL BOARD</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6722d6963193ac95</t>
+          <t>https://www.indeed.com/viewjob?jk=530025f520e267c1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Platform Engineer VI - Data Services</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Gradera</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=530025f520e267c1</t>
+          <t>https://www.indeed.com/viewjob?jk=0f26c60aecfc298d</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Hybrid)</t>
+          <t>Data Scientist Senior Associate</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Unlimited Systems</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, ECS, IAM, RDS, Azure, Scala, Kafka, Splunk</t>
+          <t>AWS, Glue, ECS, RDS, Spark, PySpark, Oracle, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e19d2be5d242f190</t>
+          <t>https://www.indeed.com/viewjob?jk=8c02b7e5e2ede6f3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Scientist Senior Associate</t>
+          <t>DevOps Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Unlimited Systems</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, RDS, Spark, PySpark, Oracle, ETL, Splunk, CI/CD</t>
+          <t>AWS, SQS, API Gateway, ECS, IAM, RDS, Azure, Scala, Kafka, Splunk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c02b7e5e2ede6f3</t>
+          <t>https://www.indeed.com/viewjob?jk=e19d2be5d242f190</t>
         </is>
       </c>
     </row>
@@ -1063,17 +1063,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Versa Networks</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,17 +1081,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Dask, Polars, MLOps, MLflow, Terraform</t>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d8fd3bb26a1e48b</t>
+          <t>https://www.indeed.com/viewjob?jk=630d48996f1eac48</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=630d48996f1eac48</t>
+          <t>https://www.indeed.com/viewjob?jk=9d7a92b5805d6137</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7a92b5805d6137</t>
+          <t>https://www.indeed.com/viewjob?jk=fd3e9bf3427fd2d6</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd3e9bf3427fd2d6</t>
+          <t>https://www.indeed.com/viewjob?jk=3ec6e06ec6b6e3fa</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ec6e06ec6b6e3fa</t>
+          <t>https://www.indeed.com/viewjob?jk=14216a18b53ccbd9</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14216a18b53ccbd9</t>
+          <t>https://www.indeed.com/viewjob?jk=c4bf15647e9f22c6</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Versa Networks</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Dask, Polars, MLOps, MLflow, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4bf15647e9f22c6</t>
+          <t>https://www.indeed.com/viewjob?jk=6d8fd3bb26a1e48b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>Senior IT Developer TDS (US)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Databricks, Scala, Kafka, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e283e1b09898d08</t>
+          <t>https://www.indeed.com/viewjob?jk=4ba9067ff8ad3678</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (33139)</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f6d6b581aa01dfb</t>
+          <t>https://www.indeed.com/viewjob?jk=8e283e1b09898d08</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior MarTech Engineer (Braze/Claude)</t>
+          <t>Senior Analytics Engineer (33139)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da2cd5f2d2247bd7</t>
+          <t>https://www.indeed.com/viewjob?jk=9f6d6b581aa01dfb</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior IT Developer TDS (US)</t>
+          <t>Senior MarTech Engineer (Braze/Claude)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Kafka, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ba9067ff8ad3678</t>
+          <t>https://www.indeed.com/viewjob?jk=da2cd5f2d2247bd7</t>
         </is>
       </c>
     </row>
@@ -1483,17 +1483,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Systems Engineer - Delivery DevOps</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, MySQL, MongoDB</t>
+          <t>AWS, RDS, BigQuery, Scala, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac326e94203a756e</t>
+          <t>https://www.indeed.com/viewjob?jk=7f60289bd7b154e2</t>
         </is>
       </c>
     </row>
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7424c005b9ced1ab</t>
+          <t>https://www.indeed.com/viewjob?jk=ac326e94203a756e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer - Delivery DevOps</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f60289bd7b154e2</t>
+          <t>https://www.indeed.com/viewjob?jk=7424c005b9ced1ab</t>
         </is>
       </c>
     </row>
@@ -1623,17 +1623,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer III - Cloud Data Platform</t>
+          <t>Sr. Software Engineer, Cloud - Analytics Platform</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, ECS, RDS, Spark, Scala, MySQL, DynamoDB, Cassandra, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26ac8e996e1bb5d6</t>
+          <t>https://www.indeed.com/viewjob?jk=ec75113b2386de94</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Cloud - Analytics Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Spark, Scala, MySQL, DynamoDB, Cassandra, NoSQL, Jenkins</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec75113b2386de94</t>
+          <t>https://www.indeed.com/viewjob?jk=4bdb09774bada084</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III - Cloud Data Platform</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bdb09774bada084</t>
+          <t>https://www.indeed.com/viewjob?jk=26ac8e996e1bb5d6</t>
         </is>
       </c>
     </row>
@@ -1833,17 +1833,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Sally Beauty</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>RDS, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcc108d020014d64</t>
+          <t>https://www.indeed.com/viewjob?jk=5832467cbe11eede</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>Software Engineer II-Python/PySpark</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13f9bc74bc5d1d66</t>
+          <t>https://www.indeed.com/viewjob?jk=bbbc18e6ff889804</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Sally Beauty</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, S3, ECS, IAM, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5832467cbe11eede</t>
+          <t>https://www.indeed.com/viewjob?jk=76545a7a26014492</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer II-Python/PySpark</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbbc18e6ff889804</t>
+          <t>https://www.indeed.com/viewjob?jk=fcc108d020014d64</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Platform &amp; Integration Engineer (Kafka)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Medica Services Company LLC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76545a7a26014492</t>
+          <t>https://www.indeed.com/viewjob?jk=1a1e479ebfe2163b</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Platform &amp; Integration Engineer (Kafka)</t>
+          <t>Senior Platform Engineer (Cloud &amp; AI Platform)- Remote within US</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Medica Services Company LLC</t>
+          <t>OEConnection</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a1e479ebfe2163b</t>
+          <t>https://www.indeed.com/viewjob?jk=024ce94c4237b353</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=024ce94c4237b353</t>
+          <t>https://www.indeed.com/viewjob?jk=e08d2c63dac884c6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Cloud &amp; AI Platform)- Remote within US</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>OEConnection</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e08d2c63dac884c6</t>
+          <t>https://www.indeed.com/viewjob?jk=13f9bc74bc5d1d66</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Agentic AI Engineer</t>
+          <t>AWS &amp; Databricks Platform Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ingram Micro</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Dask, CI/CD, Git</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fbe4faecbcb6e49</t>
+          <t>https://www.indeed.com/viewjob?jk=54ffcf229826c509</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AWS &amp; Databricks Platform Architect</t>
+          <t>Senior Java Developer with AI Experience</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54ffcf229826c509</t>
+          <t>https://www.indeed.com/viewjob?jk=c1f24944a225af1c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Java Developer with AI Experience</t>
+          <t>Senior Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Glint Tech Solutions</t>
+          <t>Ingram Micro</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1f24944a225af1c</t>
+          <t>https://www.indeed.com/viewjob?jk=1fbe4faecbcb6e49</t>
         </is>
       </c>
     </row>
@@ -2393,17 +2393,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Pre-Sales Solution Architect</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Blue Orange Digital</t>
+          <t>PURE Insurance</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>White Plains, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Snowflake, ELT, dbt</t>
+          <t>AWS, ECS, RDS, Databricks, Scala, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=148c58d976f8aa98</t>
+          <t>https://www.indeed.com/viewjob?jk=2b7ea8b8e5406480</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Pre-Sales Solution Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PURE Insurance</t>
+          <t>Blue Orange Digital</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>White Plains, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, Scala, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Snowflake, ELT, dbt</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b7ea8b8e5406480</t>
+          <t>https://www.indeed.com/viewjob?jk=148c58d976f8aa98</t>
         </is>
       </c>
     </row>
@@ -2638,17 +2638,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer II (Python/Java/AWS/Pyspark)</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Star Schema, CI/CD, Git</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git, Datadog</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee9a97ffa509cdb3</t>
+          <t>https://www.indeed.com/viewjob?jk=fb76cbe4b5a98afe</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Software Engineer II (Python/Java/AWS/Pyspark)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Alameda, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git, Datadog</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Star Schema, CI/CD, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb76cbe4b5a98afe</t>
+          <t>https://www.indeed.com/viewjob?jk=ee9a97ffa509cdb3</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-25.xlsx
+++ b/results/job_matches_2026-07-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cactus Wellhead - Data Engineer &amp; Architect</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cactus Wellhead</t>
+          <t>Gradera</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35a580479028c129</t>
+          <t>https://www.indeed.com/viewjob?jk=0f26c60aecfc298d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer- Analytics Products</t>
+          <t>Cactus Wellhead - Data Engineer &amp; Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DC PUBLIC CHARTER SCHOOL BOARD</t>
+          <t>Cactus Wellhead</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6722d6963193ac95</t>
+          <t>https://www.indeed.com/viewjob?jk=35a580479028c129</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Platform Engineer VI - Data Services</t>
+          <t>Data Engineer- Analytics Products</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>DC PUBLIC CHARTER SCHOOL BOARD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=530025f520e267c1</t>
+          <t>https://www.indeed.com/viewjob?jk=6722d6963193ac95</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Platform Engineer VI - Data Services</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Gradera</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f26c60aecfc298d</t>
+          <t>https://www.indeed.com/viewjob?jk=530025f520e267c1</t>
         </is>
       </c>
     </row>
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Data Scientist Senior Associate</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, ECS, RDS, Spark, PySpark, Oracle, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d24836d15aa901f</t>
+          <t>https://www.indeed.com/viewjob?jk=8c02b7e5e2ede6f3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Scientist Senior Associate</t>
+          <t>DevOps Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Unlimited Systems</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, RDS, Spark, PySpark, Oracle, ETL, Splunk, CI/CD</t>
+          <t>AWS, SQS, API Gateway, ECS, IAM, RDS, Azure, Scala, Kafka, Splunk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,42 +986,42 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c02b7e5e2ede6f3</t>
+          <t>https://www.indeed.com/viewjob?jk=e19d2be5d242f190</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Hybrid)</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Unlimited Systems</t>
+          <t>Versa Networks</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, ECS, IAM, RDS, Azure, Scala, Kafka, Splunk</t>
+          <t>RDS, GCP, Cloud Storage, Spark, Scala, Dask, Data Modeling, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e19d2be5d242f190</t>
+          <t>https://www.indeed.com/viewjob?jk=f6cd7a40acf5c8ea</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, GCP, Cloud Storage, Spark, Scala, Dask, Data Modeling, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Dask, Polars, MLOps, MLflow, Terraform</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6cd7a40acf5c8ea</t>
+          <t>https://www.indeed.com/viewjob?jk=6d8fd3bb26a1e48b</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Senior IT Developer TDS (US)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Versa Networks</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Dask, Polars, MLOps, MLflow, Terraform</t>
+          <t>RDS, Azure, Databricks, Scala, Kafka, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d8fd3bb26a1e48b</t>
+          <t>https://www.indeed.com/viewjob?jk=4ba9067ff8ad3678</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior IT Developer TDS (US)</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Kafka, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ba9067ff8ad3678</t>
+          <t>https://www.indeed.com/viewjob?jk=8e283e1b09898d08</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>Senior Analytics Engineer (33139)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e283e1b09898d08</t>
+          <t>https://www.indeed.com/viewjob?jk=9f6d6b581aa01dfb</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (33139)</t>
+          <t>Senior MarTech Engineer (Braze/Claude)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f6d6b581aa01dfb</t>
+          <t>https://www.indeed.com/viewjob?jk=da2cd5f2d2247bd7</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior MarTech Engineer (Braze/Claude)</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,42 +1431,42 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da2cd5f2d2247bd7</t>
+          <t>https://www.indeed.com/viewjob?jk=3949515f70fcddc9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3949515f70fcddc9</t>
+          <t>https://www.indeed.com/viewjob?jk=ac326e94203a756e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer - Delivery DevOps</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f60289bd7b154e2</t>
+          <t>https://www.indeed.com/viewjob?jk=7424c005b9ced1ab</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Systems Engineer - Delivery DevOps</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, MySQL, MongoDB</t>
+          <t>AWS, RDS, BigQuery, Scala, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac326e94203a756e</t>
+          <t>https://www.indeed.com/viewjob?jk=7f60289bd7b154e2</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Software Engineer III - Cloud Data Platform</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,59 +1581,59 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7424c005b9ced1ab</t>
+          <t>https://www.indeed.com/viewjob?jk=26ac8e996e1bb5d6</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Sr. Software Engineer, Cloud - Analytics Platform</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, ECS, RDS, Spark, Scala, MySQL, DynamoDB, Cassandra, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0600fe838e8fd40</t>
+          <t>https://www.indeed.com/viewjob?jk=ec75113b2386de94</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Cloud - Analytics Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Spark, Scala, MySQL, DynamoDB, Cassandra, NoSQL, Jenkins</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec75113b2386de94</t>
+          <t>https://www.indeed.com/viewjob?jk=4bdb09774bada084</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Cloud &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>First Orion</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>North Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, Kinesis, S3, SQS, IAM, RDS, Scala, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bdb09774bada084</t>
+          <t>https://www.indeed.com/viewjob?jk=6f4ff182033422db</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer III - Cloud Data Platform</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26ac8e996e1bb5d6</t>
+          <t>https://www.indeed.com/viewjob?jk=1b73563a16146db3</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Associate Cloud &amp; DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>First Orion</t>
+          <t>Liquidity Services, Inc.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>North Little Rock, AR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, SQS, IAM, RDS, Scala, DynamoDB, CI/CD, Terraform</t>
+          <t>AWS, Redshift, Azure, BigQuery, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f4ff182033422db</t>
+          <t>https://www.indeed.com/viewjob?jk=faf4368f99c56fa7</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b73563a16146db3</t>
+          <t>https://www.indeed.com/viewjob?jk=fcc108d020014d64</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Liquidity Services, Inc.</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, BigQuery, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf4368f99c56fa7</t>
+          <t>https://www.indeed.com/viewjob?jk=13f9bc74bc5d1d66</t>
         </is>
       </c>
     </row>
@@ -1938,17 +1938,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Platform &amp; Integration Engineer (Kafka)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Medica Services Company LLC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcc108d020014d64</t>
+          <t>https://www.indeed.com/viewjob?jk=1a1e479ebfe2163b</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Platform &amp; Integration Engineer (Kafka)</t>
+          <t>AWS &amp; Databricks Platform Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Medica Services Company LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a1e479ebfe2163b</t>
+          <t>https://www.indeed.com/viewjob?jk=54ffcf229826c509</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Cloud &amp; AI Platform)- Remote within US</t>
+          <t>Senior Java Developer with AI Experience</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>OEConnection</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=024ce94c4237b353</t>
+          <t>https://www.indeed.com/viewjob?jk=c1f24944a225af1c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Cloud &amp; AI Platform)- Remote within US</t>
+          <t>Senior Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>OEConnection</t>
+          <t>Ingram Micro</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e08d2c63dac884c6</t>
+          <t>https://www.indeed.com/viewjob?jk=1fbe4faecbcb6e49</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Simpson Strong-Tie</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13f9bc74bc5d1d66</t>
+          <t>https://www.indeed.com/viewjob?jk=b066ce08bf22f47c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AWS &amp; Databricks Platform Architect</t>
+          <t>Artificial Intelligence Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>M2S Group</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Highland Park, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54ffcf229826c509</t>
+          <t>https://www.indeed.com/viewjob?jk=dde1cd623d007554</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Java Developer with AI Experience</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Glint Tech Solutions</t>
+          <t>BGE, Inc</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1f24944a225af1c</t>
+          <t>https://www.indeed.com/viewjob?jk=54c4f37450aa9007</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Agentic AI Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ingram Micro</t>
+          <t>BGE, Inc</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Dask, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fbe4faecbcb6e49</t>
+          <t>https://www.indeed.com/viewjob?jk=1ed66eb1c43b3061</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Simpson Strong-Tie</t>
+          <t>BGE, Inc</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b066ce08bf22f47c</t>
+          <t>https://www.indeed.com/viewjob?jk=b4f5eb1da717e31e</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Architect</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>M2S Group</t>
+          <t>PURE Insurance</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Highland Park, IL, US USA</t>
+          <t>White Plains, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, ECS, RDS, Databricks, Scala, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dde1cd623d007554</t>
+          <t>https://www.indeed.com/viewjob?jk=2b7ea8b8e5406480</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BGE, Inc</t>
+          <t>Precisely</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c4f37450aa9007</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3498d244cd3dd0</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Java AWS Software Engineer III</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BGE, Inc</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ed66eb1c43b3061</t>
+          <t>https://www.indeed.com/viewjob?jk=7e88dcde57fa9ced</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BGE, Inc</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, Azure, Scala, SQL Server, MySQL, ETL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4f5eb1da717e31e</t>
+          <t>https://www.indeed.com/viewjob?jk=77de33f1323a932a</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PURE Insurance</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>White Plains, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, Scala, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, Azure, Scala, SQL Server, MySQL, ETL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,67 +2421,67 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b7ea8b8e5406480</t>
+          <t>https://www.indeed.com/viewjob?jk=fca0033255b9f7dc</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Pre-Sales Solution Architect</t>
+          <t>Data DevOps Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Blue Orange Digital</t>
+          <t>Versa Networks</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Snowflake, ELT, dbt</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, Jenkins, Terraform, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=148c58d976f8aa98</t>
+          <t>https://www.indeed.com/viewjob?jk=6e80fc4f1c8a9728</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer II (Python/Java/AWS/Pyspark)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Precisely</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Star Schema, CI/CD, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3498d244cd3dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=ee9a97ffa509cdb3</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Java AWS Software Engineer III</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git, Datadog</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e88dcde57fa9ced</t>
+          <t>https://www.indeed.com/viewjob?jk=fb76cbe4b5a98afe</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>Axogen</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, MySQL, ETL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Fact Tables, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,59 +2561,59 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77de33f1323a932a</t>
+          <t>https://www.indeed.com/viewjob?jk=24d477b9eaa3792d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Data Analyst / Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, MySQL, ETL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fca0033255b9f7dc</t>
+          <t>https://www.indeed.com/viewjob?jk=9fb24a781dd0a7af</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data DevOps Engineer</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Versa Networks</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, Jenkins, Terraform, Jenkins, Git, Python</t>
+          <t>RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e80fc4f1c8a9728</t>
+          <t>https://www.indeed.com/viewjob?jk=099ab57136f08627</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>DERMS Data Architect &amp; Integration</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>GE Vernova</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Alameda, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git, Datadog</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb76cbe4b5a98afe</t>
+          <t>https://www.indeed.com/viewjob?jk=381bad2f60317342</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer II (Python/Java/AWS/Pyspark)</t>
+          <t>Business Informatics Support Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Trillium Health Resources</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Star Schema, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee9a97ffa509cdb3</t>
+          <t>https://www.indeed.com/viewjob?jk=c1bc5a017b98965e</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Business Informatics Support Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Axogen</t>
+          <t>Trillium Health Resources</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Fact Tables, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24d477b9eaa3792d</t>
+          <t>https://www.indeed.com/viewjob?jk=61b3b18503d4acec</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Analyst / Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fb24a781dd0a7af</t>
+          <t>https://www.indeed.com/viewjob?jk=935ece4128fe6f9f</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>Great Gray Trust Company</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, Docker, SonarQube, Git, Python</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=099ab57136f08627</t>
+          <t>https://www.indeed.com/viewjob?jk=6d12b3ac28ec908f</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>DERMS Data Architect &amp; Integration</t>
+          <t>Backend Python Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GE Vernova</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>California City, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=381bad2f60317342</t>
+          <t>https://www.indeed.com/viewjob?jk=a8ab8761ac03ae1e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Business Informatics Support Data Engineer</t>
+          <t>Software Engineer – Full Stack</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Trillium Health Resources</t>
+          <t>Empower Pharmacy</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1bc5a017b98965e</t>
+          <t>https://www.indeed.com/viewjob?jk=e06173fc3c6ce8f8</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Business Informatics Support Data Engineer</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Trillium Health Resources</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61b3b18503d4acec</t>
+          <t>https://www.indeed.com/viewjob?jk=e0047e52c4d67e20</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=935ece4128fe6f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=b91b81ba111bb33b</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Great Gray Trust Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, Docker, SonarQube, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d12b3ac28ec908f</t>
+          <t>https://www.indeed.com/viewjob?jk=7afb773581c3b4c0</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer – Full Stack</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Empower Pharmacy</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06173fc3c6ce8f8</t>
+          <t>https://www.indeed.com/viewjob?jk=95650589278c6f55</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3050,146 +3050,6 @@
         </is>
       </c>
       <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e0047e52c4d67e20</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II - Encore Program</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b91b81ba111bb33b</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II - Encore Program</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7afb773581c3b4c0</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II - Encore Program</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Hermitage, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=95650589278c6f55</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II - Encore Program</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=e2f93e37daf3e792</t>
         </is>

--- a/results/job_matches_2026-07-25.xlsx
+++ b/results/job_matches_2026-07-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Associate Cloud &amp; DevOps Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>First Orion</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>North Little Rock, AR, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, SQS, IAM, RDS, Scala, DynamoDB, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f4ff182033422db</t>
+          <t>https://www.indeed.com/viewjob?jk=1b73563a16146db3</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Liquidity Services, Inc.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Redshift, Azure, BigQuery, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b73563a16146db3</t>
+          <t>https://www.indeed.com/viewjob?jk=faf4368f99c56fa7</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Liquidity Services, Inc.</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, BigQuery, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf4368f99c56fa7</t>
+          <t>https://www.indeed.com/viewjob?jk=13f9bc74bc5d1d66</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Sally Beauty</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>RDS, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcc108d020014d64</t>
+          <t>https://www.indeed.com/viewjob?jk=5832467cbe11eede</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>Software Engineer II-Python/PySpark</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13f9bc74bc5d1d66</t>
+          <t>https://www.indeed.com/viewjob?jk=bbbc18e6ff889804</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Sally Beauty</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, S3, ECS, IAM, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5832467cbe11eede</t>
+          <t>https://www.indeed.com/viewjob?jk=76545a7a26014492</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer II-Python/PySpark</t>
+          <t>AWS &amp; Databricks Platform Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbbc18e6ff889804</t>
+          <t>https://www.indeed.com/viewjob?jk=54ffcf229826c509</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Mulesoft Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76545a7a26014492</t>
+          <t>https://www.indeed.com/viewjob?jk=08f9a00d6c95207e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Platform &amp; Integration Engineer (Kafka)</t>
+          <t>Senior Java Developer with AI Experience</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Medica Services Company LLC</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a1e479ebfe2163b</t>
+          <t>https://www.indeed.com/viewjob?jk=c1f24944a225af1c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AWS &amp; Databricks Platform Architect</t>
+          <t>Senior Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Ingram Micro</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54ffcf229826c509</t>
+          <t>https://www.indeed.com/viewjob?jk=1fbe4faecbcb6e49</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Java Developer with AI Experience</t>
+          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Glint Tech Solutions</t>
+          <t>Simpson Strong-Tie</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1f24944a225af1c</t>
+          <t>https://www.indeed.com/viewjob?jk=b066ce08bf22f47c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Agentic AI Engineer</t>
+          <t>Artificial Intelligence Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ingram Micro</t>
+          <t>M2S Group</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Highland Park, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Dask, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fbe4faecbcb6e49</t>
+          <t>https://www.indeed.com/viewjob?jk=dde1cd623d007554</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Simpson Strong-Tie</t>
+          <t>BGE, Inc</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b066ce08bf22f47c</t>
+          <t>https://www.indeed.com/viewjob?jk=54c4f37450aa9007</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Architect</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>M2S Group</t>
+          <t>BGE, Inc</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Highland Park, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dde1cd623d007554</t>
+          <t>https://www.indeed.com/viewjob?jk=1ed66eb1c43b3061</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c4f37450aa9007</t>
+          <t>https://www.indeed.com/viewjob?jk=b4f5eb1da717e31e</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BGE, Inc</t>
+          <t>Precisely</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ed66eb1c43b3061</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3498d244cd3dd0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Java AWS Software Engineer III</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BGE, Inc</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4f5eb1da717e31e</t>
+          <t>https://www.indeed.com/viewjob?jk=7e88dcde57fa9ced</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PURE Insurance</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>White Plains, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, Scala, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, Azure, Scala, SQL Server, MySQL, ETL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b7ea8b8e5406480</t>
+          <t>https://www.indeed.com/viewjob?jk=77de33f1323a932a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Precisely</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, SQL Server, MySQL, ETL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3498d244cd3dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=fca0033255b9f7dc</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Java AWS Software Engineer III</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>PURE Insurance</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>White Plains, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, ECS, RDS, Databricks, Scala, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,67 +2351,67 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e88dcde57fa9ced</t>
+          <t>https://www.indeed.com/viewjob?jk=2b7ea8b8e5406480</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Data DevOps Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>Versa Networks</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, MySQL, ETL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, Jenkins, Terraform, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77de33f1323a932a</t>
+          <t>https://www.indeed.com/viewjob?jk=6e80fc4f1c8a9728</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Software Engineer II (Python/Java/AWS/Pyspark)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, MySQL, ETL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Star Schema, CI/CD, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fca0033255b9f7dc</t>
+          <t>https://www.indeed.com/viewjob?jk=ee9a97ffa509cdb3</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data DevOps Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Versa Networks</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, Jenkins, Terraform, Jenkins, Git, Python</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git, Datadog</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e80fc4f1c8a9728</t>
+          <t>https://www.indeed.com/viewjob?jk=fb76cbe4b5a98afe</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer II (Python/Java/AWS/Pyspark)</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Axogen</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Star Schema, CI/CD, Git</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Fact Tables, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee9a97ffa509cdb3</t>
+          <t>https://www.indeed.com/viewjob?jk=24d477b9eaa3792d</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Analyst / Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Alameda, CA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git, Datadog</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb76cbe4b5a98afe</t>
+          <t>https://www.indeed.com/viewjob?jk=9fb24a781dd0a7af</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Axogen</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Fact Tables, Power BI, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24d477b9eaa3792d</t>
+          <t>https://www.indeed.com/viewjob?jk=099ab57136f08627</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Analyst / Engineer</t>
+          <t>DERMS Data Architect &amp; Integration</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>GE Vernova</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fb24a781dd0a7af</t>
+          <t>https://www.indeed.com/viewjob?jk=381bad2f60317342</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Business Informatics Support Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>Trillium Health Resources</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=099ab57136f08627</t>
+          <t>https://www.indeed.com/viewjob?jk=c1bc5a017b98965e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DERMS Data Architect &amp; Integration</t>
+          <t>Business Informatics Support Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GE Vernova</t>
+          <t>Trillium Health Resources</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=381bad2f60317342</t>
+          <t>https://www.indeed.com/viewjob?jk=61b3b18503d4acec</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Business Informatics Support Data Engineer</t>
+          <t>Backend Python Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Trillium Health Resources</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>California City, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1bc5a017b98965e</t>
+          <t>https://www.indeed.com/viewjob?jk=a8ab8761ac03ae1e</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Business Informatics Support Data Engineer</t>
+          <t>Software Engineer – Full Stack</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Trillium Health Resources</t>
+          <t>Empower Pharmacy</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61b3b18503d4acec</t>
+          <t>https://www.indeed.com/viewjob?jk=e06173fc3c6ce8f8</t>
         </is>
       </c>
     </row>
@@ -2778,17 +2778,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Great Gray Trust Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, Docker, SonarQube, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d12b3ac28ec908f</t>
+          <t>https://www.indeed.com/viewjob?jk=e0047e52c4d67e20</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Backend Python Engineer</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>California City, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8ab8761ac03ae1e</t>
+          <t>https://www.indeed.com/viewjob?jk=b91b81ba111bb33b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer – Full Stack</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Empower Pharmacy</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06173fc3c6ce8f8</t>
+          <t>https://www.indeed.com/viewjob?jk=7afb773581c3b4c0</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0047e52c4d67e20</t>
+          <t>https://www.indeed.com/viewjob?jk=95650589278c6f55</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2945,111 +2945,6 @@
         </is>
       </c>
       <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b91b81ba111bb33b</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II - Encore Program</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7afb773581c3b4c0</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II - Encore Program</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Hermitage, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=95650589278c6f55</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II - Encore Program</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=e2f93e37daf3e792</t>
         </is>

--- a/results/job_matches_2026-07-25.xlsx
+++ b/results/job_matches_2026-07-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,25 +783,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Platform Engineer VI - Data Services</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>TAIT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Lititz, PA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=530025f520e267c1</t>
+          <t>https://www.indeed.com/viewjob?jk=54cfb968de0a9abd</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data engineer (Power BI)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TAIT</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lititz, PA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54cfb968de0a9abd</t>
+          <t>https://www.indeed.com/viewjob?jk=b1c4bb478a10661f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data engineer (Power BI)</t>
+          <t>Data Scientist Senior Associate</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Snowflake, Oracle</t>
+          <t>AWS, Glue, ECS, RDS, Spark, PySpark, Oracle, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1c4bb478a10661f</t>
+          <t>https://www.indeed.com/viewjob?jk=8c02b7e5e2ede6f3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pyx Health</t>
+          <t>Unlimited Systems</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, SQS, API Gateway, ECS, IAM, RDS, Azure, Scala, Kafka, Splunk</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,94 +916,94 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea50071b5800db9</t>
+          <t>https://www.indeed.com/viewjob?jk=e19d2be5d242f190</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Scientist Senior Associate</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Versa Networks</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, RDS, Spark, PySpark, Oracle, ETL, Splunk, CI/CD</t>
+          <t>RDS, GCP, Cloud Storage, Spark, Scala, Dask, Data Modeling, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c02b7e5e2ede6f3</t>
+          <t>https://www.indeed.com/viewjob?jk=f6cd7a40acf5c8ea</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Hybrid)</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Unlimited Systems</t>
+          <t>Versa Networks</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, ECS, IAM, RDS, Azure, Scala, Kafka, Splunk</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Dask, Polars, MLOps, MLflow, Terraform</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e19d2be5d242f190</t>
+          <t>https://www.indeed.com/viewjob?jk=6d8fd3bb26a1e48b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Versa Networks</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, GCP, Cloud Storage, Spark, Scala, Dask, Data Modeling, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6cd7a40acf5c8ea</t>
+          <t>https://www.indeed.com/viewjob?jk=630d48996f1eac48</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Versa Networks</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Dask, Polars, MLOps, MLflow, Terraform</t>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d8fd3bb26a1e48b</t>
+          <t>https://www.indeed.com/viewjob?jk=9d7a92b5805d6137</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=630d48996f1eac48</t>
+          <t>https://www.indeed.com/viewjob?jk=fd3e9bf3427fd2d6</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7a92b5805d6137</t>
+          <t>https://www.indeed.com/viewjob?jk=3ec6e06ec6b6e3fa</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd3e9bf3427fd2d6</t>
+          <t>https://www.indeed.com/viewjob?jk=14216a18b53ccbd9</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ec6e06ec6b6e3fa</t>
+          <t>https://www.indeed.com/viewjob?jk=c4bf15647e9f22c6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior IT Developer TDS (US)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Scala, Kafka, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14216a18b53ccbd9</t>
+          <t>https://www.indeed.com/viewjob?jk=4ba9067ff8ad3678</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4bf15647e9f22c6</t>
+          <t>https://www.indeed.com/viewjob?jk=8e283e1b09898d08</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior IT Developer TDS (US)</t>
+          <t>Senior Analytics Engineer (33139)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Kafka, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ba9067ff8ad3678</t>
+          <t>https://www.indeed.com/viewjob?jk=9f6d6b581aa01dfb</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>Senior MarTech Engineer (Braze/Claude)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e283e1b09898d08</t>
+          <t>https://www.indeed.com/viewjob?jk=da2cd5f2d2247bd7</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (33139)</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,77 +1361,77 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f6d6b581aa01dfb</t>
+          <t>https://www.indeed.com/viewjob?jk=3949515f70fcddc9</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior MarTech Engineer (Braze/Claude)</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da2cd5f2d2247bd7</t>
+          <t>https://www.indeed.com/viewjob?jk=ac326e94203a756e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3949515f70fcddc9</t>
+          <t>https://www.indeed.com/viewjob?jk=7424c005b9ced1ab</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Software Engineer III - Cloud Data Platform</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,54 +1476,54 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac326e94203a756e</t>
+          <t>https://www.indeed.com/viewjob?jk=26ac8e996e1bb5d6</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Sr. Software Engineer, Cloud - Analytics Platform</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, MySQL, MongoDB</t>
+          <t>AWS, ECS, RDS, Spark, Scala, MySQL, DynamoDB, Cassandra, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7424c005b9ced1ab</t>
+          <t>https://www.indeed.com/viewjob?jk=ec75113b2386de94</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer - Delivery DevOps</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1532,11 +1532,11 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f60289bd7b154e2</t>
+          <t>https://www.indeed.com/viewjob?jk=4bdb09774bada084</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer III - Cloud Data Platform</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,102 +1581,102 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26ac8e996e1bb5d6</t>
+          <t>https://www.indeed.com/viewjob?jk=1b73563a16146db3</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Cloud - Analytics Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Liquidity Services, Inc.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Spark, Scala, MySQL, DynamoDB, Cassandra, NoSQL, Jenkins</t>
+          <t>AWS, Redshift, Azure, BigQuery, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec75113b2386de94</t>
+          <t>https://www.indeed.com/viewjob?jk=faf4368f99c56fa7</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bdb09774bada084</t>
+          <t>https://www.indeed.com/viewjob?jk=13f9bc74bc5d1d66</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Sally Beauty</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b73563a16146db3</t>
+          <t>https://www.indeed.com/viewjob?jk=5832467cbe11eede</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II-Python/PySpark</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Liquidity Services, Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, BigQuery, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf4368f99c56fa7</t>
+          <t>https://www.indeed.com/viewjob?jk=bbbc18e6ff889804</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>AWS &amp; Databricks Platform Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13f9bc74bc5d1d66</t>
+          <t>https://www.indeed.com/viewjob?jk=54ffcf229826c509</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Mulesoft Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Sally Beauty</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5832467cbe11eede</t>
+          <t>https://www.indeed.com/viewjob?jk=08f9a00d6c95207e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer II-Python/PySpark</t>
+          <t>Senior Java Developer with AI Experience</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbbc18e6ff889804</t>
+          <t>https://www.indeed.com/viewjob?jk=c1f24944a225af1c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Ingram Micro</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76545a7a26014492</t>
+          <t>https://www.indeed.com/viewjob?jk=1fbe4faecbcb6e49</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AWS &amp; Databricks Platform Architect</t>
+          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Simpson Strong-Tie</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54ffcf229826c509</t>
+          <t>https://www.indeed.com/viewjob?jk=b066ce08bf22f47c</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Mulesoft Developer</t>
+          <t>Artificial Intelligence Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>M2S Group</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Highland Park, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08f9a00d6c95207e</t>
+          <t>https://www.indeed.com/viewjob?jk=dde1cd623d007554</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Java Developer with AI Experience</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Glint Tech Solutions</t>
+          <t>BGE, Inc</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1f24944a225af1c</t>
+          <t>https://www.indeed.com/viewjob?jk=54c4f37450aa9007</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Agentic AI Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ingram Micro</t>
+          <t>BGE, Inc</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Dask, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fbe4faecbcb6e49</t>
+          <t>https://www.indeed.com/viewjob?jk=1ed66eb1c43b3061</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Simpson Strong-Tie</t>
+          <t>BGE, Inc</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b066ce08bf22f47c</t>
+          <t>https://www.indeed.com/viewjob?jk=b4f5eb1da717e31e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>M2S Group</t>
+          <t>Precisely</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Highland Park, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dde1cd623d007554</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3498d244cd3dd0</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Java AWS Software Engineer III</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BGE, Inc</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c4f37450aa9007</t>
+          <t>https://www.indeed.com/viewjob?jk=7e88dcde57fa9ced</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BGE, Inc</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, Azure, Scala, SQL Server, MySQL, ETL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ed66eb1c43b3061</t>
+          <t>https://www.indeed.com/viewjob?jk=77de33f1323a932a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BGE, Inc</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, Azure, Scala, SQL Server, MySQL, ETL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,49 +2176,49 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4f5eb1da717e31e</t>
+          <t>https://www.indeed.com/viewjob?jk=fca0033255b9f7dc</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data DevOps Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Precisely</t>
+          <t>Versa Networks</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, Jenkins, Terraform, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3498d244cd3dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=6e80fc4f1c8a9728</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Java AWS Software Engineer III</t>
+          <t>Software Engineer II (Python/Java/AWS/Pyspark)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2228,15 +2228,15 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Star Schema, CI/CD, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e88dcde57fa9ced</t>
+          <t>https://www.indeed.com/viewjob?jk=ee9a97ffa509cdb3</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, MySQL, ETL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git, Datadog</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77de33f1323a932a</t>
+          <t>https://www.indeed.com/viewjob?jk=fb76cbe4b5a98afe</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Axogen</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, MySQL, ETL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Fact Tables, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,59 +2316,59 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fca0033255b9f7dc</t>
+          <t>https://www.indeed.com/viewjob?jk=24d477b9eaa3792d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Analyst / Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PURE Insurance</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>White Plains, NY, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, Scala, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b7ea8b8e5406480</t>
+          <t>https://www.indeed.com/viewjob?jk=9fb24a781dd0a7af</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data DevOps Engineer</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Versa Networks</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, Jenkins, Terraform, Jenkins, Git, Python</t>
+          <t>RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e80fc4f1c8a9728</t>
+          <t>https://www.indeed.com/viewjob?jk=099ab57136f08627</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer II (Python/Java/AWS/Pyspark)</t>
+          <t>DERMS Data Architect &amp; Integration</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GE Vernova</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Star Schema, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee9a97ffa509cdb3</t>
+          <t>https://www.indeed.com/viewjob?jk=381bad2f60317342</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Business Informatics Support Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Trillium Health Resources</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Alameda, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git, Datadog</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb76cbe4b5a98afe</t>
+          <t>https://www.indeed.com/viewjob?jk=c1bc5a017b98965e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Business Informatics Support Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Axogen</t>
+          <t>Trillium Health Resources</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Fact Tables, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24d477b9eaa3792d</t>
+          <t>https://www.indeed.com/viewjob?jk=61b3b18503d4acec</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Analyst / Engineer</t>
+          <t>Backend Python Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>California City, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fb24a781dd0a7af</t>
+          <t>https://www.indeed.com/viewjob?jk=a8ab8761ac03ae1e</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Software Engineer – Full Stack</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>Empower Pharmacy</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=099ab57136f08627</t>
+          <t>https://www.indeed.com/viewjob?jk=e06173fc3c6ce8f8</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DERMS Data Architect &amp; Integration</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>GE Vernova</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=381bad2f60317342</t>
+          <t>https://www.indeed.com/viewjob?jk=e0047e52c4d67e20</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Business Informatics Support Data Engineer</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Trillium Health Resources</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1bc5a017b98965e</t>
+          <t>https://www.indeed.com/viewjob?jk=b91b81ba111bb33b</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Business Informatics Support Data Engineer</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Trillium Health Resources</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61b3b18503d4acec</t>
+          <t>https://www.indeed.com/viewjob?jk=7afb773581c3b4c0</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Backend Python Engineer</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>California City, CA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8ab8761ac03ae1e</t>
+          <t>https://www.indeed.com/viewjob?jk=95650589278c6f55</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer – Full Stack</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Empower Pharmacy</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2735,216 +2735,6 @@
         </is>
       </c>
       <c r="G66" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e06173fc3c6ce8f8</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Mastercard</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>O'Fallon, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, Git</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=935ece4128fe6f9f</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II - Encore Program</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e0047e52c4d67e20</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II - Encore Program</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b91b81ba111bb33b</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II - Encore Program</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7afb773581c3b4c0</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II - Encore Program</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Hermitage, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=95650589278c6f55</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II - Encore Program</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=e2f93e37daf3e792</t>
         </is>

--- a/results/job_matches_2026-07-25.xlsx
+++ b/results/job_matches_2026-07-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DevOps Engineer Live Streaming- Wixom, MI</t>
+          <t>Sr. Engineer, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>J&amp;B Medical</t>
+          <t>Lovesac</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Wixom, MI, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP, Scala</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Medallion Architecture, BigQuery, Dataflow, Spark, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41ea01c619cf5f4e</t>
+          <t>https://www.indeed.com/viewjob?jk=2d666b2674d51e46</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Data &amp; Analytics</t>
+          <t>Senior DataOps Engineer ( Remote US)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lovesac</t>
+          <t>Smile Digital Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Medallion Architecture, BigQuery, Dataflow, Spark, PySpark</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Spark, Scala, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,19 +601,19 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d666b2674d51e46</t>
+          <t>https://www.indeed.com/viewjob?jk=b9cf29eaf2fb3e62</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior DataOps Engineer ( Remote US)</t>
+          <t>Senior Data Engineer (33142)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Smile Digital Health</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -626,69 +626,69 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Spark, Scala, DataOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9cf29eaf2fb3e62</t>
+          <t>https://www.indeed.com/viewjob?jk=614b737b604716f8</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (33142)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>Gradera</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=614b737b604716f8</t>
+          <t>https://www.indeed.com/viewjob?jk=0f26c60aecfc298d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Cactus Wellhead - Data Engineer &amp; Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Gradera</t>
+          <t>Cactus Wellhead</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f26c60aecfc298d</t>
+          <t>https://www.indeed.com/viewjob?jk=35a580479028c129</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cactus Wellhead - Data Engineer &amp; Architect</t>
+          <t>Data Engineer- Analytics Products</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cactus Wellhead</t>
+          <t>DC PUBLIC CHARTER SCHOOL BOARD</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,42 +731,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35a580479028c129</t>
+          <t>https://www.indeed.com/viewjob?jk=6722d6963193ac95</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer- Analytics Products</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DC PUBLIC CHARTER SCHOOL BOARD</t>
+          <t>TAIT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lititz, PA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6722d6963193ac95</t>
+          <t>https://www.indeed.com/viewjob?jk=54cfb968de0a9abd</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Scientist Senior Associate</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TAIT</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lititz, PA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Glue, ECS, RDS, Spark, PySpark, Oracle, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54cfb968de0a9abd</t>
+          <t>https://www.indeed.com/viewjob?jk=8c02b7e5e2ede6f3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data engineer (Power BI)</t>
+          <t>DevOps Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Unlimited Systems</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Snowflake, Oracle</t>
+          <t>AWS, SQS, API Gateway, ECS, IAM, RDS, Azure, Scala, Kafka, Splunk</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,94 +846,94 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1c4bb478a10661f</t>
+          <t>https://www.indeed.com/viewjob?jk=e19d2be5d242f190</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Scientist Senior Associate</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Versa Networks</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, RDS, Spark, PySpark, Oracle, ETL, Splunk, CI/CD</t>
+          <t>RDS, GCP, Cloud Storage, Spark, Scala, Dask, Data Modeling, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c02b7e5e2ede6f3</t>
+          <t>https://www.indeed.com/viewjob?jk=f6cd7a40acf5c8ea</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Hybrid)</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Unlimited Systems</t>
+          <t>Versa Networks</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, ECS, IAM, RDS, Azure, Scala, Kafka, Splunk</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Dask, Polars, MLOps, MLflow, Terraform</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e19d2be5d242f190</t>
+          <t>https://www.indeed.com/viewjob?jk=6d8fd3bb26a1e48b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Versa Networks</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, GCP, Cloud Storage, Spark, Scala, Dask, Data Modeling, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6cd7a40acf5c8ea</t>
+          <t>https://www.indeed.com/viewjob?jk=630d48996f1eac48</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Senior IT Developer TDS (US)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Versa Networks</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Dask, Polars, MLOps, MLflow, Terraform</t>
+          <t>RDS, Azure, Databricks, Scala, Kafka, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d8fd3bb26a1e48b</t>
+          <t>https://www.indeed.com/viewjob?jk=4ba9067ff8ad3678</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=630d48996f1eac48</t>
+          <t>https://www.indeed.com/viewjob?jk=8e283e1b09898d08</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Analytics Engineer (33139)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7a92b5805d6137</t>
+          <t>https://www.indeed.com/viewjob?jk=9f6d6b581aa01dfb</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior MarTech Engineer (Braze/Claude)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,42 +1081,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd3e9bf3427fd2d6</t>
+          <t>https://www.indeed.com/viewjob?jk=da2cd5f2d2247bd7</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ec6e06ec6b6e3fa</t>
+          <t>https://www.indeed.com/viewjob?jk=ac326e94203a756e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14216a18b53ccbd9</t>
+          <t>https://www.indeed.com/viewjob?jk=7424c005b9ced1ab</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - Cloud Data Platform</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,19 +1196,19 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4bf15647e9f22c6</t>
+          <t>https://www.indeed.com/viewjob?jk=26ac8e996e1bb5d6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior IT Developer TDS (US)</t>
+          <t>Sr. Software Engineer, Cloud - Analytics Platform</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1217,46 +1217,46 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Kafka, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, ECS, RDS, Spark, Scala, MySQL, DynamoDB, Cassandra, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ba9067ff8ad3678</t>
+          <t>https://www.indeed.com/viewjob?jk=ec75113b2386de94</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,137 +1266,137 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e283e1b09898d08</t>
+          <t>https://www.indeed.com/viewjob?jk=4bdb09774bada084</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (33139)</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f6d6b581aa01dfb</t>
+          <t>https://www.indeed.com/viewjob?jk=1b73563a16146db3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior MarTech Engineer (Braze/Claude)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Liquidity Services, Inc.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Redshift, Azure, BigQuery, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da2cd5f2d2247bd7</t>
+          <t>https://www.indeed.com/viewjob?jk=faf4368f99c56fa7</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3949515f70fcddc9</t>
+          <t>https://www.indeed.com/viewjob?jk=13f9bc74bc5d1d66</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Sally Beauty</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, MySQL, MongoDB</t>
+          <t>RDS, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac326e94203a756e</t>
+          <t>https://www.indeed.com/viewjob?jk=5832467cbe11eede</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Software Engineer II-Python/PySpark</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, MySQL, MongoDB</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7424c005b9ced1ab</t>
+          <t>https://www.indeed.com/viewjob?jk=bbbc18e6ff889804</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer III - Cloud Data Platform</t>
+          <t>AWS &amp; Databricks Platform Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,67 +1476,67 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26ac8e996e1bb5d6</t>
+          <t>https://www.indeed.com/viewjob?jk=54ffcf229826c509</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Cloud - Analytics Platform</t>
+          <t>Mulesoft Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Spark, Scala, MySQL, DynamoDB, Cassandra, NoSQL, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec75113b2386de94</t>
+          <t>https://www.indeed.com/viewjob?jk=08f9a00d6c95207e</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Java Developer with AI Experience</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bdb09774bada084</t>
+          <t>https://www.indeed.com/viewjob?jk=c1f24944a225af1c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Ingram Micro</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b73563a16146db3</t>
+          <t>https://www.indeed.com/viewjob?jk=1fbe4faecbcb6e49</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Liquidity Services, Inc.</t>
+          <t>Simpson Strong-Tie</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, BigQuery, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf4368f99c56fa7</t>
+          <t>https://www.indeed.com/viewjob?jk=b066ce08bf22f47c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>Artificial Intelligence Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>M2S Group</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Highland Park, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13f9bc74bc5d1d66</t>
+          <t>https://www.indeed.com/viewjob?jk=dde1cd623d007554</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Sally Beauty</t>
+          <t>Precisely</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,14 +1686,14 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5832467cbe11eede</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3498d244cd3dd0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer II-Python/PySpark</t>
+          <t>Java AWS Software Engineer III</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,67 +1721,67 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbbc18e6ff889804</t>
+          <t>https://www.indeed.com/viewjob?jk=7e88dcde57fa9ced</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AWS &amp; Databricks Platform Architect</t>
+          <t>Data DevOps Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Versa Networks</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, ETL, ELT</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, Jenkins, Terraform, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54ffcf229826c509</t>
+          <t>https://www.indeed.com/viewjob?jk=6e80fc4f1c8a9728</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Mulesoft Developer</t>
+          <t>Software Engineer II (Python/Java/AWS/Pyspark)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Star Schema, CI/CD, Git</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08f9a00d6c95207e</t>
+          <t>https://www.indeed.com/viewjob?jk=ee9a97ffa509cdb3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Java Developer with AI Experience</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Glint Tech Solutions</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps, CI/CD</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git, Datadog</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,67 +1826,67 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1f24944a225af1c</t>
+          <t>https://www.indeed.com/viewjob?jk=fb76cbe4b5a98afe</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Agentic AI Engineer</t>
+          <t>Data Analyst / Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ingram Micro</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Dask, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fbe4faecbcb6e49</t>
+          <t>https://www.indeed.com/viewjob?jk=9fb24a781dd0a7af</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Simpson Strong-Tie</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,67 +1896,67 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b066ce08bf22f47c</t>
+          <t>https://www.indeed.com/viewjob?jk=099ab57136f08627</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Architect</t>
+          <t>Backend Python Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>M2S Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Highland Park, IL, US USA</t>
+          <t>California City, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dde1cd623d007554</t>
+          <t>https://www.indeed.com/viewjob?jk=a8ab8761ac03ae1e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BGE, Inc</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c4f37450aa9007</t>
+          <t>https://www.indeed.com/viewjob?jk=e0047e52c4d67e20</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BGE, Inc</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ed66eb1c43b3061</t>
+          <t>https://www.indeed.com/viewjob?jk=b91b81ba111bb33b</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BGE, Inc</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4f5eb1da717e31e</t>
+          <t>https://www.indeed.com/viewjob?jk=7afb773581c3b4c0</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Precisely</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3498d244cd3dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=95650589278c6f55</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Java AWS Software Engineer III</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2105,636 +2105,6 @@
         </is>
       </c>
       <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e88dcde57fa9ced</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>LexisNexis Risk Solutions</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, SQL Server, MySQL, ETL, CI/CD, Jenkins, GitHub Actions, Docker</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=77de33f1323a932a</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>RELX Group</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, SQL Server, MySQL, ETL, CI/CD, Jenkins, GitHub Actions, Docker</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fca0033255b9f7dc</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Data DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Versa Networks</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Santa Clara, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, Jenkins, Terraform, Jenkins, Git, Python</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6e80fc4f1c8a9728</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Software Engineer II (Python/Java/AWS/Pyspark)</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Star Schema, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ee9a97ffa509cdb3</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Senior Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Abbott</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Alameda, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fb76cbe4b5a98afe</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Sr. Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Axogen</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Fact Tables, Power BI, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24d477b9eaa3792d</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Data Analyst / Engineer</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>McAfee</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Frisco, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9fb24a781dd0a7af</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Schneider Electric</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=099ab57136f08627</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>DERMS Data Architect &amp; Integration</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>GE Vernova</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=381bad2f60317342</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Business Informatics Support Data Engineer</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Trillium Health Resources</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c1bc5a017b98965e</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Business Informatics Support Data Engineer</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Trillium Health Resources</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=61b3b18503d4acec</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Backend Python Engineer</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>California City, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a8ab8761ac03ae1e</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Software Engineer – Full Stack</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Empower Pharmacy</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e06173fc3c6ce8f8</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II - Encore Program</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e0047e52c4d67e20</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II - Encore Program</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b91b81ba111bb33b</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II - Encore Program</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7afb773581c3b4c0</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II - Encore Program</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Hermitage, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=95650589278c6f55</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II - Encore Program</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=e2f93e37daf3e792</t>
         </is>

--- a/results/job_matches_2026-07-25.xlsx
+++ b/results/job_matches_2026-07-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1168,17 +1168,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer III - Cloud Data Platform</t>
+          <t>Sr. Software Engineer, Cloud - Analytics Platform</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Guidewire</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, ECS, RDS, Spark, Scala, MySQL, DynamoDB, Cassandra, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26ac8e996e1bb5d6</t>
+          <t>https://www.indeed.com/viewjob?jk=ec75113b2386de94</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Cloud - Analytics Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Spark, Scala, MySQL, DynamoDB, Cassandra, NoSQL, Jenkins</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec75113b2386de94</t>
+          <t>https://www.indeed.com/viewjob?jk=4bdb09774bada084</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bdb09774bada084</t>
+          <t>https://www.indeed.com/viewjob?jk=1b73563a16146db3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Liquidity Services, Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Redshift, Azure, BigQuery, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b73563a16146db3</t>
+          <t>https://www.indeed.com/viewjob?jk=faf4368f99c56fa7</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Liquidity Services, Inc.</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, BigQuery, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf4368f99c56fa7</t>
+          <t>https://www.indeed.com/viewjob?jk=13f9bc74bc5d1d66</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Sally Beauty</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
+          <t>RDS, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13f9bc74bc5d1d66</t>
+          <t>https://www.indeed.com/viewjob?jk=5832467cbe11eede</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II-Python/PySpark</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sally Beauty</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5832467cbe11eede</t>
+          <t>https://www.indeed.com/viewjob?jk=bbbc18e6ff889804</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer II-Python/PySpark</t>
+          <t>AWS &amp; Databricks Platform Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbbc18e6ff889804</t>
+          <t>https://www.indeed.com/viewjob?jk=54ffcf229826c509</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AWS &amp; Databricks Platform Architect</t>
+          <t>Mulesoft Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54ffcf229826c509</t>
+          <t>https://www.indeed.com/viewjob?jk=08f9a00d6c95207e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Mulesoft Developer</t>
+          <t>Senior Java Developer with AI Experience</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08f9a00d6c95207e</t>
+          <t>https://www.indeed.com/viewjob?jk=c1f24944a225af1c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Java Developer with AI Experience</t>
+          <t>Senior Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Glint Tech Solutions</t>
+          <t>Ingram Micro</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1f24944a225af1c</t>
+          <t>https://www.indeed.com/viewjob?jk=1fbe4faecbcb6e49</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Agentic AI Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ingram Micro</t>
+          <t>Precisely</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Dask, CI/CD, Git</t>
+          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fbe4faecbcb6e49</t>
+          <t>https://www.indeed.com/viewjob?jk=9d3498d244cd3dd0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
+          <t>Java AWS Software Engineer III</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Simpson Strong-Tie</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,67 +1616,67 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b066ce08bf22f47c</t>
+          <t>https://www.indeed.com/viewjob?jk=7e88dcde57fa9ced</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Architect</t>
+          <t>Data DevOps Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>M2S Group</t>
+          <t>Versa Networks</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Highland Park, IL, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, Jenkins, Terraform, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dde1cd623d007554</t>
+          <t>https://www.indeed.com/viewjob?jk=6e80fc4f1c8a9728</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer II (Python/Java/AWS/Pyspark)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Precisely</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Star Schema, CI/CD, Git</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3498d244cd3dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=ee9a97ffa509cdb3</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Java AWS Software Engineer III</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git, Datadog</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e88dcde57fa9ced</t>
+          <t>https://www.indeed.com/viewjob?jk=fb76cbe4b5a98afe</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data DevOps Engineer</t>
+          <t>Data Analyst / Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Versa Networks</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, Jenkins, Terraform, Jenkins, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e80fc4f1c8a9728</t>
+          <t>https://www.indeed.com/viewjob?jk=9fb24a781dd0a7af</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer II (Python/Java/AWS/Pyspark)</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Star Schema, CI/CD, Git</t>
+          <t>RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee9a97ffa509cdb3</t>
+          <t>https://www.indeed.com/viewjob?jk=099ab57136f08627</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Backend Python Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Alameda, CA, US USA</t>
+          <t>California City, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git, Datadog</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb76cbe4b5a98afe</t>
+          <t>https://www.indeed.com/viewjob?jk=a8ab8761ac03ae1e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Analyst / Engineer</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fb24a781dd0a7af</t>
+          <t>https://www.indeed.com/viewjob?jk=e0047e52c4d67e20</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=099ab57136f08627</t>
+          <t>https://www.indeed.com/viewjob?jk=b91b81ba111bb33b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Backend Python Engineer</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>California City, CA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,17 +1921,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8ab8761ac03ae1e</t>
+          <t>https://www.indeed.com/viewjob?jk=7afb773581c3b4c0</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0047e52c4d67e20</t>
+          <t>https://www.indeed.com/viewjob?jk=95650589278c6f55</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2000,111 +2000,6 @@
         </is>
       </c>
       <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b91b81ba111bb33b</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II - Encore Program</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7afb773581c3b4c0</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II - Encore Program</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Hermitage, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=95650589278c6f55</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II - Encore Program</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=e2f93e37daf3e792</t>
         </is>

--- a/results/job_matches_2026-07-25.xlsx
+++ b/results/job_matches_2026-07-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer III-Databricks</t>
+          <t>Sr. Engineer, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Lovesac</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, Medallion Architecture, BigQuery, Dataflow, Spark, PySpark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=097f3e8cd3b1164b</t>
+          <t>https://www.indeed.com/viewjob?jk=2d666b2674d51e46</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Data &amp; Analytics</t>
+          <t>Senior DataOps Engineer ( Remote US)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lovesac</t>
+          <t>Smile Digital Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, Medallion Architecture, BigQuery, Dataflow, Spark, PySpark</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Spark, Scala, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,19 +566,19 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d666b2674d51e46</t>
+          <t>https://www.indeed.com/viewjob?jk=b9cf29eaf2fb3e62</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior DataOps Engineer ( Remote US)</t>
+          <t>Senior Data Engineer (33142)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Smile Digital Health</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -591,69 +591,69 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Spark, Scala, DataOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9cf29eaf2fb3e62</t>
+          <t>https://www.indeed.com/viewjob?jk=614b737b604716f8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (33142)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>Gradera</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=614b737b604716f8</t>
+          <t>https://www.indeed.com/viewjob?jk=0f26c60aecfc298d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Cactus Wellhead - Data Engineer &amp; Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Gradera</t>
+          <t>Cactus Wellhead</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f26c60aecfc298d</t>
+          <t>https://www.indeed.com/viewjob?jk=35a580479028c129</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cactus Wellhead - Data Engineer &amp; Architect</t>
+          <t>Data Engineer- Analytics Products</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cactus Wellhead</t>
+          <t>DC PUBLIC CHARTER SCHOOL BOARD</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,42 +696,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35a580479028c129</t>
+          <t>https://www.indeed.com/viewjob?jk=6722d6963193ac95</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer- Analytics Products</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DC PUBLIC CHARTER SCHOOL BOARD</t>
+          <t>TAIT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lititz, PA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6722d6963193ac95</t>
+          <t>https://www.indeed.com/viewjob?jk=54cfb968de0a9abd</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TAIT</t>
+          <t>Unlimited Systems</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lititz, PA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, SQS, API Gateway, ECS, IAM, RDS, Azure, Scala, Kafka, Splunk</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,94 +776,94 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54cfb968de0a9abd</t>
+          <t>https://www.indeed.com/viewjob?jk=e19d2be5d242f190</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Scientist Senior Associate</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Versa Networks</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, RDS, Spark, PySpark, Oracle, ETL, Splunk, CI/CD</t>
+          <t>RDS, GCP, Cloud Storage, Spark, Scala, Dask, Data Modeling, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c02b7e5e2ede6f3</t>
+          <t>https://www.indeed.com/viewjob?jk=f6cd7a40acf5c8ea</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Hybrid)</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Unlimited Systems</t>
+          <t>Versa Networks</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, ECS, IAM, RDS, Azure, Scala, Kafka, Splunk</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Dask, Polars, MLOps, MLflow, Terraform</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e19d2be5d242f190</t>
+          <t>https://www.indeed.com/viewjob?jk=6d8fd3bb26a1e48b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Versa Networks</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, GCP, Cloud Storage, Spark, Scala, Dask, Data Modeling, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6cd7a40acf5c8ea</t>
+          <t>https://www.indeed.com/viewjob?jk=630d48996f1eac48</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Versa Networks</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Dask, Polars, MLOps, MLflow, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d8fd3bb26a1e48b</t>
+          <t>https://www.indeed.com/viewjob?jk=8e283e1b09898d08</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Analytics Engineer (33139)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=630d48996f1eac48</t>
+          <t>https://www.indeed.com/viewjob?jk=9f6d6b581aa01dfb</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior IT Developer TDS (US)</t>
+          <t>Senior MarTech Engineer (Braze/Claude)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,42 +976,42 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Kafka, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ba9067ff8ad3678</t>
+          <t>https://www.indeed.com/viewjob?jk=da2cd5f2d2247bd7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,102 +1021,102 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e283e1b09898d08</t>
+          <t>https://www.indeed.com/viewjob?jk=ac326e94203a756e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (33139)</t>
+          <t>Sr. Software Engineer, Cloud - Analytics Platform</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, ECS, RDS, Spark, Scala, MySQL, DynamoDB, Cassandra, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f6d6b581aa01dfb</t>
+          <t>https://www.indeed.com/viewjob?jk=ec75113b2386de94</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior MarTech Engineer (Braze/Claude)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Scala, MLOps, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da2cd5f2d2247bd7</t>
+          <t>https://www.indeed.com/viewjob?jk=4bdb09774bada084</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac326e94203a756e</t>
+          <t>https://www.indeed.com/viewjob?jk=1b73563a16146db3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Liquidity Services, Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, MySQL, MongoDB</t>
+          <t>AWS, Redshift, Azure, BigQuery, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,42 +1161,42 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7424c005b9ced1ab</t>
+          <t>https://www.indeed.com/viewjob?jk=faf4368f99c56fa7</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Cloud - Analytics Platform</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Spark, Scala, MySQL, DynamoDB, Cassandra, NoSQL, Jenkins</t>
+          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec75113b2386de94</t>
+          <t>https://www.indeed.com/viewjob?jk=13f9bc74bc5d1d66</t>
         </is>
       </c>
     </row>
@@ -1208,20 +1208,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Sally Beauty</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
+          <t>RDS, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Git</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bdb09774bada084</t>
+          <t>https://www.indeed.com/viewjob?jk=5832467cbe11eede</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>AWS &amp; Databricks Platform Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b73563a16146db3</t>
+          <t>https://www.indeed.com/viewjob?jk=54ffcf229826c509</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Mulesoft Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Liquidity Services, Inc.</t>
+          <t>Centurion Consulting Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, BigQuery, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf4368f99c56fa7</t>
+          <t>https://www.indeed.com/viewjob?jk=08f9a00d6c95207e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>Senior Java Developer with AI Experience</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, GCP, Hadoop, Spark, Scala, Kafka, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13f9bc74bc5d1d66</t>
+          <t>https://www.indeed.com/viewjob?jk=c1f24944a225af1c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sally Beauty</t>
+          <t>Ingram Micro</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Dask, CI/CD, Git</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,67 +1371,67 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5832467cbe11eede</t>
+          <t>https://www.indeed.com/viewjob?jk=1fbe4faecbcb6e49</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer II-Python/PySpark</t>
+          <t>Data DevOps Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Versa Networks</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, Jenkins, Terraform, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbbc18e6ff889804</t>
+          <t>https://www.indeed.com/viewjob?jk=6e80fc4f1c8a9728</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AWS &amp; Databricks Platform Architect</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git, Datadog</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,67 +1441,67 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54ffcf229826c509</t>
+          <t>https://www.indeed.com/viewjob?jk=fb76cbe4b5a98afe</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Mulesoft Developer</t>
+          <t>Data Analyst / Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Centurion Consulting Group</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08f9a00d6c95207e</t>
+          <t>https://www.indeed.com/viewjob?jk=9fb24a781dd0a7af</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Java Developer with AI Experience</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Glint Tech Solutions</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, MLOps, CI/CD</t>
+          <t>RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,67 +1511,67 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1f24944a225af1c</t>
+          <t>https://www.indeed.com/viewjob?jk=099ab57136f08627</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Agentic AI Engineer</t>
+          <t>Backend Python Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ingram Micro</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>California City, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Dask, CI/CD, Git</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fbe4faecbcb6e49</t>
+          <t>https://www.indeed.com/viewjob?jk=a8ab8761ac03ae1e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Precisely</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d3498d244cd3dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=e0047e52c4d67e20</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Java AWS Software Engineer III</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e88dcde57fa9ced</t>
+          <t>https://www.indeed.com/viewjob?jk=b91b81ba111bb33b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data DevOps Engineer</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Versa Networks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, Jenkins, Terraform, Jenkins, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e80fc4f1c8a9728</t>
+          <t>https://www.indeed.com/viewjob?jk=7afb773581c3b4c0</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer II (Python/Java/AWS/Pyspark)</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Star Schema, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee9a97ffa509cdb3</t>
+          <t>https://www.indeed.com/viewjob?jk=95650589278c6f55</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Alameda, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Git, Datadog</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1720,286 +1720,6 @@
         </is>
       </c>
       <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fb76cbe4b5a98afe</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Data Analyst / Engineer</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>McAfee</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Frisco, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9fb24a781dd0a7af</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Schneider Electric</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=099ab57136f08627</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Backend Python Engineer</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>California City, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a8ab8761ac03ae1e</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II - Encore Program</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e0047e52c4d67e20</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II - Encore Program</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b91b81ba111bb33b</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II - Encore Program</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7afb773581c3b4c0</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II - Encore Program</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Hermitage, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=95650589278c6f55</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II - Encore Program</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=e2f93e37daf3e792</t>
         </is>
